--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34205,6 +34205,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1472">
+      <c r="A1472" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1472" t="n">
+        <v>29000</v>
+      </c>
+      <c r="C1472" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1472" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1472" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1472" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1472" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34228,6 +34228,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1473">
+      <c r="A1473" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1473" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C1473" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D1473" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1473" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1473" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G1473" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34251,6 +34251,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1474">
+      <c r="A1474" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1474" t="n">
+        <v>12000</v>
+      </c>
+      <c r="C1474" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1474" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E1474" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1474" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1474" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34274,6 +34274,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1475">
+      <c r="A1475" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1475" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1475" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1475" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1475" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1475" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1475" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34115,22 +34115,22 @@
     </row>
     <row r="1468">
       <c r="A1468" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1468" t="n">
-        <v>18000</v>
+        <v>8000</v>
       </c>
       <c r="C1468" t="n">
-        <v>3.14000010490417</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="D1468" t="n">
-        <v>3.09999990463257</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="E1468" t="n">
-        <v>3.09999990463257</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="F1468" t="n">
-        <v>3.09999990463257</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G1468" t="s">
         <v>7</v>
@@ -34138,10 +34138,10 @@
     </row>
     <row r="1469">
       <c r="A1469" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1469" t="n">
-        <v>13000</v>
+        <v>18000</v>
       </c>
       <c r="C1469" t="n">
         <v>3.14000010490417</v>
@@ -34153,7 +34153,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="F1469" t="n">
-        <v>3.11999988555908</v>
+        <v>3.09999990463257</v>
       </c>
       <c r="G1469" t="s">
         <v>7</v>
@@ -34161,22 +34161,22 @@
     </row>
     <row r="1470">
       <c r="A1470" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1470" t="n">
-        <v>5000</v>
+        <v>13000</v>
       </c>
       <c r="C1470" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="D1470" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1470" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1470" t="n">
         <v>3.11999988555908</v>
-      </c>
-      <c r="D1470" t="n">
-        <v>3.05999994277954</v>
-      </c>
-      <c r="E1470" t="n">
-        <v>3.11999988555908</v>
-      </c>
-      <c r="F1470" t="n">
-        <v>3.05999994277954</v>
       </c>
       <c r="G1470" t="s">
         <v>7</v>
@@ -34184,19 +34184,19 @@
     </row>
     <row r="1471">
       <c r="A1471" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1471" t="n">
-        <v>3000</v>
+        <v>5000</v>
       </c>
       <c r="C1471" t="n">
-        <v>3.09999990463257</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="D1471" t="n">
         <v>3.05999994277954</v>
       </c>
       <c r="E1471" t="n">
-        <v>3.09999990463257</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="F1471" t="n">
         <v>3.05999994277954</v>
@@ -34207,22 +34207,22 @@
     </row>
     <row r="1472">
       <c r="A1472" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1472" t="n">
-        <v>29000</v>
+        <v>3000</v>
       </c>
       <c r="C1472" t="n">
-        <v>3.14000010490417</v>
+        <v>3.09999990463257</v>
       </c>
       <c r="D1472" t="n">
-        <v>3.07999992370605</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="E1472" t="n">
         <v>3.09999990463257</v>
       </c>
       <c r="F1472" t="n">
-        <v>3.07999992370605</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="G1472" t="s">
         <v>7</v>
@@ -34230,22 +34230,22 @@
     </row>
     <row r="1473">
       <c r="A1473" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1473" t="n">
-        <v>3000</v>
+        <v>29000</v>
       </c>
       <c r="C1473" t="n">
-        <v>3.09999990463257</v>
+        <v>3.14000010490417</v>
       </c>
       <c r="D1473" t="n">
         <v>3.07999992370605</v>
       </c>
       <c r="E1473" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1473" t="n">
         <v>3.07999992370605</v>
-      </c>
-      <c r="F1473" t="n">
-        <v>3.09999990463257</v>
       </c>
       <c r="G1473" t="s">
         <v>7</v>
@@ -34253,22 +34253,22 @@
     </row>
     <row r="1474">
       <c r="A1474" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1474" t="n">
-        <v>12000</v>
+        <v>3000</v>
       </c>
       <c r="C1474" t="n">
-        <v>3.11999988555908</v>
+        <v>3.09999990463257</v>
       </c>
       <c r="D1474" t="n">
         <v>3.07999992370605</v>
       </c>
       <c r="E1474" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1474" t="n">
         <v>3.09999990463257</v>
-      </c>
-      <c r="F1474" t="n">
-        <v>3.07999992370605</v>
       </c>
       <c r="G1474" t="s">
         <v>7</v>
@@ -34276,24 +34276,47 @@
     </row>
     <row r="1475">
       <c r="A1475" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1475" t="n">
-        <v>9000</v>
+        <v>12000</v>
       </c>
       <c r="C1475" t="n">
-        <v>3.14000010490417</v>
+        <v>3.11999988555908</v>
       </c>
       <c r="D1475" t="n">
-        <v>3.09999990463257</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="E1475" t="n">
         <v>3.09999990463257</v>
       </c>
       <c r="F1475" t="n">
-        <v>3.14000010490417</v>
+        <v>3.07999992370605</v>
       </c>
       <c r="G1475" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1476">
+      <c r="A1476" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1476" t="n">
+        <v>8000</v>
+      </c>
+      <c r="C1476" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1476" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E1476" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F1476" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G1476" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695139408112</v>
+        <v>1.56695127487183</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56516051292419</v>
+        <v>1.56516063213348</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G25" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G30" t="n">
-        <v>1.50427329540253</v>
+        <v>1.50427341461182</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G33" t="n">
-        <v>1.52665829658508</v>
+        <v>1.52665841579437</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G54" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G56" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G64" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G66" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G74" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G75" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>1.47293436527252</v>
+        <v>1.47293424606323</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G88" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829044342041</v>
+        <v>1.59829032421112</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.1847779750824</v>
+        <v>2.18477773666382</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>2.11314582824707</v>
+        <v>2.11314558982849</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>2.06837606430054</v>
+        <v>2.06837582588196</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674391746521</v>
+        <v>1.9967440366745</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>2.65934014320374</v>
+        <v>2.65934038162231</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561656951904</v>
+        <v>2.60561633110046</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980037689209</v>
+        <v>2.56980013847351</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -38800,6 +38800,32 @@
         <v>3.09999990463257</v>
       </c>
       <c r="H1478" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1479">
+      <c r="A1479" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1479" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C1479" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1479" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="E1479" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1479" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1479" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="H1479" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54134285449982</v>
+        <v>1.54134297370911</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695127487183</v>
+        <v>1.56695139408112</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54456651210785</v>
+        <v>1.54456639289856</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G11" t="n">
-        <v>1.54456651210785</v>
+        <v>1.54456639289856</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G12" t="n">
-        <v>1.54456651210785</v>
+        <v>1.54456639289856</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G15" t="n">
-        <v>1.54456651210785</v>
+        <v>1.54456639289856</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51770436763763</v>
+        <v>1.51770448684692</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G25" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>1.51322734355927</v>
+        <v>1.51322746276855</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G32" t="n">
-        <v>1.53561234474182</v>
+        <v>1.53561246395111</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G34" t="n">
-        <v>1.54456651210785</v>
+        <v>1.54456639289856</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G41" t="n">
-        <v>1.51770436763763</v>
+        <v>1.51770448684692</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>1.41025638580322</v>
+        <v>1.41025626659393</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G56" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G64" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G66" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G74" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G75" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G88" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.18477773666382</v>
+        <v>2.1847779750824</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>2.11314558982849</v>
+        <v>2.11314582824707</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9967440366745</v>
+        <v>1.99674355983734</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.05942177772522</v>
+        <v>2.0594220161438</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.21164011955261</v>
+        <v>2.21163988113403</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281203269958</v>
+        <v>2.37281227111816</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.41758227348328</v>
+        <v>2.4175820350647</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.310133934021</v>
+        <v>2.31013417243958</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G121" t="n">
-        <v>2.56084632873535</v>
+        <v>2.56084609031677</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G126" t="n">
-        <v>2.56084632873535</v>
+        <v>2.56084609031677</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235203742981</v>
+        <v>2.46235227584839</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56084632873535</v>
+        <v>2.56084609031677</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638150215149</v>
+        <v>3.01638126373291</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981905937195</v>
+        <v>2.97981929779053</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -38826,6 +38826,32 @@
         <v>3.03999996185303</v>
       </c>
       <c r="H1479" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1480">
+      <c r="A1480" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1480" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1480" t="n">
+        <v>3</v>
+      </c>
+      <c r="H1480" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -473,7 +473,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56516063213348</v>
+        <v>1.56516051292419</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G6" t="n">
-        <v>1.54456639289856</v>
+        <v>1.54456651210785</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G11" t="n">
-        <v>1.54456639289856</v>
+        <v>1.54456651210785</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G12" t="n">
-        <v>1.54456639289856</v>
+        <v>1.54456651210785</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G15" t="n">
-        <v>1.54456639289856</v>
+        <v>1.54456651210785</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51770448684692</v>
+        <v>1.51770436763763</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891721725464</v>
+        <v>1.37891709804535</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>1.51322746276855</v>
+        <v>1.51322734355927</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G30" t="n">
-        <v>1.50427341461182</v>
+        <v>1.50427329540253</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G32" t="n">
-        <v>1.53561246395111</v>
+        <v>1.53561234474182</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G34" t="n">
-        <v>1.54456639289856</v>
+        <v>1.54456651210785</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G41" t="n">
-        <v>1.51770448684692</v>
+        <v>1.51770436763763</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829032421112</v>
+        <v>1.59829044342041</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419178009033</v>
+        <v>2.10419201850891</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674355983734</v>
+        <v>1.99674379825592</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G110" t="n">
-        <v>2.21163988113403</v>
+        <v>2.21164011955261</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G121" t="n">
-        <v>2.56084609031677</v>
+        <v>2.56084632873535</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G126" t="n">
-        <v>2.56084609031677</v>
+        <v>2.56084632873535</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G138" t="n">
-        <v>2.56084609031677</v>
+        <v>2.56084632873535</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638126373291</v>
+        <v>3.01638150215149</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981929779053</v>
+        <v>2.97981905937195</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -38852,6 +38852,32 @@
         <v>3</v>
       </c>
       <c r="H1480" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1481">
+      <c r="A1481" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1481" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C1481" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D1481" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1481" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F1481" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G1481" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H1481" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -38881,6 +38881,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1482">
+      <c r="A1482" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1482" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C1482" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D1482" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1482" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1482" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1482" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="H1482" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695139408112</v>
+        <v>1.56695127487183</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56516051292419</v>
+        <v>1.56516063213348</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G25" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G30" t="n">
-        <v>1.50427329540253</v>
+        <v>1.50427341461182</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G33" t="n">
-        <v>1.52665829658508</v>
+        <v>1.52665841579437</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G54" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G56" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G64" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G66" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473340988159</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G74" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G75" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>1.47293436527252</v>
+        <v>1.47293424606323</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G88" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829044342041</v>
+        <v>1.59829032421112</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.1847779750824</v>
+        <v>2.18477773666382</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>2.11314582824707</v>
+        <v>2.11314558982849</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>2.06837606430054</v>
+        <v>2.06837582588196</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674391746521</v>
+        <v>1.9967440366745</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>2.65934014320374</v>
+        <v>2.65934038162231</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561656951904</v>
+        <v>2.60561633110046</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980037689209</v>
+        <v>2.56980013847351</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -38956,6 +38956,32 @@
         <v>2.79999995231628</v>
       </c>
       <c r="H1484" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1485">
+      <c r="A1485" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1485" t="n">
+        <v>42000</v>
+      </c>
+      <c r="C1485" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="D1485" t="n">
+        <v>2.6800000667572</v>
+      </c>
+      <c r="E1485" t="n">
+        <v>2.77999997138977</v>
+      </c>
+      <c r="F1485" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="G1485" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="H1485" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34589,8 +34589,31 @@
       <c r="E1488" t="n">
         <v>2.96000003814697</v>
       </c>
-      <c r="F1488"/>
+      <c r="F1488" t="n">
+        <v>2.96000003814697</v>
+      </c>
       <c r="G1488" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1489">
+      <c r="A1489" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1489" t="n">
+        <v>5000</v>
+      </c>
+      <c r="C1489" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D1489" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E1489" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="F1489"/>
+      <c r="G1489" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34612,8 +34612,31 @@
       <c r="E1489" t="n">
         <v>2.96000003814697</v>
       </c>
-      <c r="F1489"/>
+      <c r="F1489" t="n">
+        <v>2.98000001907349</v>
+      </c>
       <c r="G1489" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1490">
+      <c r="A1490" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1490" t="n">
+        <v>22000</v>
+      </c>
+      <c r="C1490" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D1490" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E1490" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F1490"/>
+      <c r="G1490" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34635,8 +34635,31 @@
       <c r="E1490" t="n">
         <v>2.98000001907349</v>
       </c>
-      <c r="F1490"/>
+      <c r="F1490" t="n">
+        <v>2.88000011444092</v>
+      </c>
       <c r="G1490" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1491">
+      <c r="A1491" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1491" t="n">
+        <v>9000</v>
+      </c>
+      <c r="C1491" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1491" t="n">
+        <v>2.79999995231628</v>
+      </c>
+      <c r="E1491" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1491"/>
+      <c r="G1491" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34658,8 +34658,31 @@
       <c r="E1491" t="n">
         <v>2.85999989509583</v>
       </c>
-      <c r="F1491"/>
+      <c r="F1491" t="n">
+        <v>2.79999995231628</v>
+      </c>
       <c r="G1491" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1492">
+      <c r="A1492" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1492" t="n">
+        <v>48000</v>
+      </c>
+      <c r="C1492" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D1492" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="E1492" t="n">
+        <v>2.8199999332428</v>
+      </c>
+      <c r="F1492"/>
+      <c r="G1492" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -34688,6 +34688,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1493">
+      <c r="A1493" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1493" t="n">
+        <v>41000</v>
+      </c>
+      <c r="C1493" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D1493" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1493" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1493" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G1493" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54134285449982</v>
+        <v>1.54134297370911</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695127487183</v>
+        <v>1.56695151329041</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56516063213348</v>
+        <v>1.56516051292419</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5535204410553</v>
+        <v>1.55352032184601</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5535204410553</v>
+        <v>1.55352032184601</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G25" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G30" t="n">
-        <v>1.50427341461182</v>
+        <v>1.50427329540253</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G31" t="n">
-        <v>1.49979627132416</v>
+        <v>1.49979639053345</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G38" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G46" t="n">
-        <v>1.39234817028046</v>
+        <v>1.39234828948975</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.39234817028046</v>
+        <v>1.39234828948975</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>1.41025638580322</v>
+        <v>1.41025626659393</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G56" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G64" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G66" t="n">
-        <v>1.40577936172485</v>
+        <v>1.40577924251556</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.4147332906723</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G74" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G75" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G88" t="n">
-        <v>1.45054936408997</v>
+        <v>1.45054924488068</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G98" t="n">
-        <v>1.57590544223785</v>
+        <v>1.57590532302856</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000773429871</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>2.11314558982849</v>
+        <v>2.11314582824707</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.9967440366745</v>
+        <v>1.99674391746521</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000773429871</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281203269958</v>
+        <v>2.37281227111816</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.310133934021</v>
+        <v>2.31013417243958</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.47130632400513</v>
+        <v>2.47130608558655</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G120" t="n">
-        <v>2.5250301361084</v>
+        <v>2.52503037452698</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57875442504883</v>
+        <v>2.57875418663025</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561633110046</v>
+        <v>2.60561656951904</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>2.57875442504883</v>
+        <v>2.57875418663025</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980013847351</v>
+        <v>2.56980037689209</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.5250301361084</v>
+        <v>2.52503037452698</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G139" t="n">
-        <v>2.5250301361084</v>
+        <v>2.52503037452698</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.47130632400513</v>
+        <v>2.47130608558655</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638150215149</v>
+        <v>3.01638126373291</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981905937195</v>
+        <v>2.97981929779053</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -39242,6 +39242,32 @@
         <v>2.92000007629395</v>
       </c>
       <c r="H1495" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1496">
+      <c r="A1496" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1496" t="n">
+        <v>34000</v>
+      </c>
+      <c r="C1496" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1496" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1496" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1496" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G1496" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H1496" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -447,7 +447,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695151329041</v>
+        <v>1.56695139408112</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891721725464</v>
+        <v>1.37891709804535</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G31" t="n">
-        <v>1.49979639053345</v>
+        <v>1.49979627132416</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G38" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G46" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829032421112</v>
+        <v>1.59829044342041</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G98" t="n">
-        <v>1.57590532302856</v>
+        <v>1.57590544223785</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000773429871</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.18477773666382</v>
+        <v>2.1847779750824</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419178009033</v>
+        <v>2.10419201850891</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674391746521</v>
+        <v>1.99674379825592</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.05942177772522</v>
+        <v>2.0594220161438</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000773429871</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.41758227348328</v>
+        <v>2.4175820350647</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G120" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561656951904</v>
+        <v>2.60561633110046</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980037689209</v>
+        <v>2.56980013847351</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235203742981</v>
+        <v>2.46235227584839</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G139" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638126373291</v>
+        <v>3.01638150215149</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981929779053</v>
+        <v>2.97981905937195</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -39268,6 +39268,32 @@
         <v>2.98000001907349</v>
       </c>
       <c r="H1496" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1497">
+      <c r="A1497" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1497" t="n">
+        <v>31000</v>
+      </c>
+      <c r="C1497" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D1497" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1497" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1497" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G1497" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H1497" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -43791,6 +43791,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1498">
+      <c r="A1498" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1498" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1498" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D1498" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1498" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="F1498" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="G1498" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="H1498" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I1498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1499">
+      <c r="A1499" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1499" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1499" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D1499" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1499" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F1499" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="G1499" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="H1499" t="n">
+        <v>8000</v>
+      </c>
+      <c r="I1499" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -43849,6 +43849,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1500">
+      <c r="A1500" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1500" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1500" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D1500" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="E1500" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="F1500" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G1500" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="H1500" t="n">
+        <v>27000</v>
+      </c>
+      <c r="I1500" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -43878,6 +43878,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1501">
+      <c r="A1501" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1501" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1501" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D1501" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E1501" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="F1501" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="G1501" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="H1501" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1501" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -43907,6 +43907,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1502">
+      <c r="A1502" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1502" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1502" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D1502" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="E1502" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1502" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G1502" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H1502" t="n">
+        <v>10000</v>
+      </c>
+      <c r="I1502" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695151329041</v>
+        <v>1.56695139408112</v>
       </c>
       <c r="H3" t="n">
         <v>153000</v>
@@ -514,7 +514,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H5" t="n">
         <v>45000</v>
@@ -601,7 +601,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H8" t="n">
         <v>5000</v>
@@ -630,7 +630,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H9" t="n">
         <v>5000</v>
@@ -746,7 +746,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H13" t="n">
         <v>6000</v>
@@ -862,7 +862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H17" t="n">
         <v>35000</v>
@@ -920,7 +920,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H19" t="n">
         <v>4000</v>
@@ -1007,7 +1007,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891721725464</v>
+        <v>1.37891709804535</v>
       </c>
       <c r="H22" t="n">
         <v>42000</v>
@@ -1065,7 +1065,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H24" t="n">
         <v>21000</v>
@@ -1268,7 +1268,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G31" t="n">
-        <v>1.49979639053345</v>
+        <v>1.49979627132416</v>
       </c>
       <c r="H31" t="n">
         <v>54000</v>
@@ -1384,7 +1384,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H35" t="n">
         <v>29000</v>
@@ -1413,7 +1413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H36" t="n">
         <v>11000</v>
@@ -1471,7 +1471,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G38" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H38" t="n">
         <v>29000</v>
@@ -1529,7 +1529,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1674,7 +1674,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H45" t="n">
         <v>196000</v>
@@ -1703,7 +1703,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G46" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H46" t="n">
         <v>49000</v>
@@ -1732,7 +1732,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H47" t="n">
         <v>99000</v>
@@ -1790,7 +1790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H49" t="n">
         <v>25000</v>
@@ -2022,7 +2022,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H57" t="n">
         <v>10000</v>
@@ -2138,7 +2138,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2167,7 +2167,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H62" t="n">
         <v>6000</v>
@@ -2196,7 +2196,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H63" t="n">
         <v>12000</v>
@@ -2312,7 +2312,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H71" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H72" t="n">
         <v>16000</v>
@@ -2573,7 +2573,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2660,7 +2660,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H80" t="n">
         <v>2000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2892,7 +2892,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H87" t="n">
         <v>3000</v>
@@ -3095,7 +3095,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H94" t="n">
         <v>50000</v>
@@ -3182,7 +3182,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829032421112</v>
+        <v>1.59829044342041</v>
       </c>
       <c r="H97" t="n">
         <v>51000</v>
@@ -3211,7 +3211,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G98" t="n">
-        <v>1.57590532302856</v>
+        <v>1.57590544223785</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000773429871</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="n">
         <v>526000</v>
@@ -3269,7 +3269,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.18477773666382</v>
+        <v>2.1847779750824</v>
       </c>
       <c r="H100" t="n">
         <v>722000</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419178009033</v>
+        <v>2.10419201850891</v>
       </c>
       <c r="H101" t="n">
         <v>211000</v>
@@ -3414,7 +3414,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674391746521</v>
+        <v>1.99674379825592</v>
       </c>
       <c r="H105" t="n">
         <v>24000</v>
@@ -3443,7 +3443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.05942177772522</v>
+        <v>2.0594220161438</v>
       </c>
       <c r="H106" t="n">
         <v>35000</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000773429871</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="n">
         <v>40000</v>
@@ -3646,7 +3646,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="n">
         <v>108000</v>
@@ -3675,7 +3675,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.41758227348328</v>
+        <v>2.4175820350647</v>
       </c>
       <c r="H114" t="n">
         <v>78000</v>
@@ -3762,7 +3762,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="n">
         <v>66000</v>
@@ -3791,7 +3791,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="n">
         <v>214000</v>
@@ -3820,7 +3820,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H119" t="n">
         <v>237000</v>
@@ -3849,7 +3849,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G120" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H120" t="n">
         <v>19000</v>
@@ -3965,7 +3965,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H124" t="n">
         <v>27000</v>
@@ -3994,7 +3994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="n">
         <v>47000</v>
@@ -4081,7 +4081,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="n">
         <v>13000</v>
@@ -4110,7 +4110,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561656951904</v>
+        <v>2.60561633110046</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4139,7 +4139,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H130" t="n">
         <v>21000</v>
@@ -4197,7 +4197,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980037689209</v>
+        <v>2.56980013847351</v>
       </c>
       <c r="H132" t="n">
         <v>46000</v>
@@ -4255,7 +4255,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235203742981</v>
+        <v>2.46235227584839</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="n">
         <v>50000</v>
@@ -4313,7 +4313,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H136" t="n">
         <v>40000</v>
@@ -4342,7 +4342,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="n">
         <v>92000</v>
@@ -4400,7 +4400,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G139" t="n">
-        <v>2.52503037452698</v>
+        <v>2.5250301361084</v>
       </c>
       <c r="H139" t="n">
         <v>19000</v>
@@ -4545,7 +4545,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4661,7 +4661,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H148" t="n">
         <v>71000</v>
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H149" t="n">
         <v>50000</v>
@@ -4748,7 +4748,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H151" t="n">
         <v>330000</v>
@@ -4835,7 +4835,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4980,7 +4980,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H159" t="n">
         <v>18000</v>
@@ -5009,7 +5009,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5212,7 +5212,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H169" t="n">
         <v>9000</v>
@@ -5299,7 +5299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H170" t="n">
         <v>135000</v>
@@ -5357,7 +5357,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H172" t="n">
         <v>6000</v>
@@ -5415,7 +5415,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H174" t="n">
         <v>31000</v>
@@ -5589,7 +5589,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H180" t="n">
         <v>11000</v>
@@ -5763,7 +5763,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H186" t="n">
         <v>5000</v>
@@ -5792,7 +5792,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H187" t="n">
         <v>21000</v>
@@ -5879,7 +5879,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -6082,7 +6082,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H197" t="n">
         <v>46000</v>
@@ -6140,7 +6140,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H199" t="n">
         <v>70000</v>
@@ -6169,7 +6169,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H200" t="n">
         <v>48000</v>
@@ -6314,7 +6314,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H205" t="n">
         <v>828000</v>
@@ -6372,7 +6372,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H207" t="n">
         <v>89000</v>
@@ -6517,7 +6517,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H212" t="n">
         <v>21000</v>
@@ -6575,7 +6575,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H214" t="n">
         <v>14000</v>
@@ -6604,7 +6604,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H215" t="n">
         <v>9000</v>
@@ -6633,7 +6633,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H216" t="n">
         <v>43000</v>
@@ -6952,7 +6952,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H227" t="n">
         <v>6000</v>
@@ -6981,7 +6981,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H228" t="n">
         <v>2000</v>
@@ -7126,7 +7126,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H233" t="n">
         <v>64000</v>
@@ -7329,7 +7329,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H240" t="n">
         <v>5000</v>
@@ -7358,7 +7358,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H242" t="n">
         <v>14000</v>
@@ -7416,7 +7416,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H243" t="n">
         <v>15000</v>
@@ -7445,7 +7445,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7677,7 +7677,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H252" t="n">
         <v>15000</v>
@@ -7909,7 +7909,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H260" t="n">
         <v>12000</v>
@@ -7996,7 +7996,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H263" t="n">
         <v>5000</v>
@@ -8025,7 +8025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H264" t="n">
         <v>9000</v>
@@ -8083,7 +8083,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8141,7 +8141,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H268" t="n">
         <v>23000</v>
@@ -8170,7 +8170,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H269" t="n">
         <v>11000</v>
@@ -8257,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H273" t="n">
         <v>1000</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H274" t="n">
         <v>9000</v>
@@ -8402,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H277" t="n">
         <v>14000</v>
@@ -8431,7 +8431,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H284" t="n">
         <v>100000</v>
@@ -8721,7 +8721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H288" t="n">
         <v>14000</v>
@@ -8779,7 +8779,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H290" t="n">
         <v>517000</v>
@@ -9040,7 +9040,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H299" t="n">
         <v>8000</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638126373291</v>
+        <v>3.01638150215149</v>
       </c>
       <c r="H301" t="n">
         <v>8000</v>
@@ -9127,7 +9127,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981929779053</v>
+        <v>2.97981905937195</v>
       </c>
       <c r="H302" t="n">
         <v>9000</v>
@@ -9185,7 +9185,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H304" t="n">
         <v>5000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9330,7 +9330,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H309" t="n">
         <v>134000</v>
@@ -9475,7 +9475,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H314" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H330" t="n">
         <v>13000</v>
@@ -10055,7 +10055,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H334" t="n">
         <v>39000</v>
@@ -10142,7 +10142,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H337" t="n">
         <v>4000</v>
@@ -10229,7 +10229,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H340" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H342" t="n">
         <v>4000</v>
@@ -10316,7 +10316,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10548,7 +10548,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10664,7 +10664,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H355" t="n">
         <v>8000</v>
@@ -10867,7 +10867,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H366" t="n">
         <v>3000</v>
@@ -11012,7 +11012,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H367" t="n">
         <v>4000</v>
@@ -11099,7 +11099,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11244,7 +11244,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H375" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H377" t="n">
         <v>5000</v>
@@ -11418,7 +11418,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H381" t="n">
         <v>14000</v>
@@ -11447,7 +11447,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H382" t="n">
         <v>1000</v>
@@ -11476,7 +11476,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H383" t="n">
         <v>20000</v>
@@ -11621,7 +11621,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H388" t="n">
         <v>4000</v>
@@ -11650,7 +11650,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11737,7 +11737,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H392" t="n">
         <v>3000</v>
@@ -11824,7 +11824,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -12143,7 +12143,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H406" t="n">
         <v>12000</v>
@@ -12259,7 +12259,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H410" t="n">
         <v>2000</v>
@@ -12578,7 +12578,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12665,7 +12665,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12810,7 +12810,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12839,7 +12839,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H430" t="n">
         <v>7000</v>
@@ -12868,7 +12868,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H434" t="n">
         <v>1000</v>
@@ -12984,7 +12984,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H452" t="n">
         <v>2000</v>
@@ -13825,7 +13825,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H464" t="n">
         <v>8000</v>
@@ -14405,7 +14405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H484" t="n">
         <v>10000</v>
@@ -14521,7 +14521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H488" t="n">
         <v>11000</v>
@@ -14579,7 +14579,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14782,7 +14782,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H497" t="n">
         <v>8000</v>
@@ -14811,7 +14811,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H498" t="n">
         <v>22000</v>
@@ -14840,7 +14840,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H506" t="n">
         <v>205000</v>
@@ -15072,7 +15072,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15246,7 +15246,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H513" t="n">
         <v>9000</v>
@@ -15275,7 +15275,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H514" t="n">
         <v>4000</v>
@@ -15304,7 +15304,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H515" t="n">
         <v>3000</v>
@@ -15362,7 +15362,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15565,7 +15565,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15594,7 +15594,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H535" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H536" t="n">
         <v>2000</v>
@@ -16116,7 +16116,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H543" t="n">
         <v>4000</v>
@@ -16232,7 +16232,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H547" t="n">
         <v>4000</v>
@@ -16406,7 +16406,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H553" t="n">
         <v>2000</v>
@@ -16435,7 +16435,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H580" t="n">
         <v>2000</v>
@@ -17479,7 +17479,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H590" t="n">
         <v>3000</v>
@@ -17769,7 +17769,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17827,7 +17827,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17856,7 +17856,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H603" t="n">
         <v>3000</v>
@@ -17885,7 +17885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H604" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H609" t="n">
         <v>3000</v>
@@ -18059,7 +18059,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H616" t="n">
         <v>7000</v>
@@ -18262,7 +18262,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H621" t="n">
         <v>2000</v>
@@ -18436,7 +18436,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H623" t="n">
         <v>3000</v>
@@ -18465,7 +18465,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H631" t="n">
         <v>13000</v>
@@ -18987,7 +18987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H642" t="n">
         <v>5000</v>
@@ -19074,7 +19074,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H645" t="n">
         <v>2000</v>
@@ -19103,7 +19103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H649" t="n">
         <v>9000</v>
@@ -19248,7 +19248,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H651" t="n">
         <v>3000</v>
@@ -19393,7 +19393,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H656" t="n">
         <v>5000</v>
@@ -19422,7 +19422,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H657" t="n">
         <v>7000</v>
@@ -19509,7 +19509,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H660" t="n">
         <v>1000</v>
@@ -19625,7 +19625,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H664" t="n">
         <v>2000</v>
@@ -19654,7 +19654,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H665" t="n">
         <v>7000</v>
@@ -19683,7 +19683,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H666" t="n">
         <v>2000</v>
@@ -19857,7 +19857,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H672" t="n">
         <v>1000</v>
@@ -19886,7 +19886,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H678" t="n">
         <v>2000</v>
@@ -20060,7 +20060,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -21249,7 +21249,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H720" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H731" t="n">
         <v>9000</v>
@@ -21771,7 +21771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H738" t="n">
         <v>1000</v>
@@ -21800,7 +21800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H739" t="n">
         <v>1000</v>
@@ -21858,7 +21858,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H741" t="n">
         <v>2000</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H742" t="n">
         <v>1000</v>
@@ -21916,7 +21916,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H743" t="n">
         <v>1000</v>
@@ -21945,7 +21945,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H746" t="n">
         <v>1000</v>
@@ -22032,7 +22032,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H747" t="n">
         <v>1000</v>
@@ -22061,7 +22061,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H752" t="n">
         <v>7000</v>
@@ -22206,7 +22206,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H756" t="n">
         <v>5000</v>
@@ -22322,7 +22322,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H760" t="n">
         <v>7000</v>
@@ -22902,7 +22902,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H777" t="n">
         <v>15000</v>
@@ -23105,7 +23105,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H784" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H787" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H789" t="n">
         <v>23000</v>
@@ -23395,7 +23395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H794" t="n">
         <v>4000</v>
@@ -23424,7 +23424,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H795" t="n">
         <v>5000</v>
@@ -23453,7 +23453,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H797" t="n">
         <v>1000</v>
@@ -23511,7 +23511,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H798" t="n">
         <v>2000</v>
@@ -23540,7 +23540,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H799" t="n">
         <v>1000</v>
@@ -23569,7 +23569,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H800" t="n">
         <v>2000</v>
@@ -23627,7 +23627,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H802" t="n">
         <v>31000</v>
@@ -23743,7 +23743,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H806" t="n">
         <v>1000</v>
@@ -24091,7 +24091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H819" t="n">
         <v>0</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H820" t="n">
         <v>12000</v>
@@ -24468,7 +24468,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H832" t="n">
         <v>67000</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H839" t="n">
         <v>13000</v>
@@ -24729,7 +24729,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24961,7 +24961,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H848" t="n">
         <v>4000</v>
@@ -24990,7 +24990,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H856" t="n">
         <v>13000</v>
@@ -25280,7 +25280,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H859" t="n">
         <v>32000</v>
@@ -25309,7 +25309,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H860" t="n">
         <v>2000</v>
@@ -25367,7 +25367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H862" t="n">
         <v>5000</v>
@@ -25744,7 +25744,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25860,7 +25860,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H879" t="n">
         <v>4000</v>
@@ -26092,7 +26092,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H887" t="n">
         <v>3000</v>
@@ -26121,7 +26121,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H889" t="n">
         <v>5000</v>
@@ -26266,7 +26266,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H893" t="n">
         <v>1000</v>
@@ -26295,7 +26295,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H899" t="n">
         <v>2000</v>
@@ -26556,7 +26556,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H903" t="n">
         <v>1000</v>
@@ -26585,7 +26585,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H907" t="n">
         <v>72000</v>
@@ -26730,7 +26730,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -27078,7 +27078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H921" t="n">
         <v>5000</v>
@@ -27107,7 +27107,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H924" t="n">
         <v>1000</v>
@@ -27194,7 +27194,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H930" t="n">
         <v>3000</v>
@@ -27368,7 +27368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H932" t="n">
         <v>1000</v>
@@ -27426,7 +27426,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27571,7 +27571,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H938" t="n">
         <v>2000</v>
@@ -27600,7 +27600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H961" t="n">
         <v>3000</v>
@@ -28267,7 +28267,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -28325,7 +28325,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -28412,7 +28412,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -28441,7 +28441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -28470,7 +28470,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H969" t="n">
         <v>1000</v>
@@ -28499,7 +28499,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -28528,7 +28528,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H971" t="n">
         <v>14000</v>
@@ -28557,7 +28557,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28818,7 +28818,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H981" t="n">
         <v>9000</v>
@@ -28963,7 +28963,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H986" t="n">
         <v>4000</v>
@@ -29079,7 +29079,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H990" t="n">
         <v>27000</v>
@@ -29108,7 +29108,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H991" t="n">
         <v>18000</v>
@@ -29224,7 +29224,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H995" t="n">
         <v>21000</v>
@@ -29253,7 +29253,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H996" t="n">
         <v>2000</v>
@@ -29282,7 +29282,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H997" t="n">
         <v>1000</v>
@@ -29311,7 +29311,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1001" t="n">
         <v>19000</v>
@@ -29514,7 +29514,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H1005" t="n">
         <v>11000</v>
@@ -29543,7 +29543,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1006" t="n">
         <v>5000</v>
@@ -29572,7 +29572,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1007" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1010" t="n">
         <v>7000</v>
@@ -30123,7 +30123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1026" t="n">
         <v>50000</v>
@@ -30210,7 +30210,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1029" t="n">
         <v>11000</v>
@@ -30297,7 +30297,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1032" t="n">
         <v>20000</v>
@@ -30326,7 +30326,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1033" t="n">
         <v>6000</v>
@@ -30355,7 +30355,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1034" t="n">
         <v>12000</v>
@@ -30442,7 +30442,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1048" t="n">
         <v>22000</v>
@@ -30790,7 +30790,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1049" t="n">
         <v>40000</v>
@@ -30964,7 +30964,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1055" t="n">
         <v>7000</v>
@@ -31341,7 +31341,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1068" t="n">
         <v>30000</v>
@@ -31399,7 +31399,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1070" t="n">
         <v>13000</v>
@@ -31428,7 +31428,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -31689,7 +31689,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1080" t="n">
         <v>4000</v>
@@ -31747,7 +31747,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1082" t="n">
         <v>2000</v>
@@ -31776,7 +31776,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1083" t="n">
         <v>10000</v>
@@ -31892,7 +31892,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1087" t="n">
         <v>39000</v>
@@ -31921,7 +31921,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1088" t="n">
         <v>45000</v>
@@ -31950,7 +31950,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1089" t="n">
         <v>19000</v>
@@ -31979,7 +31979,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1090" t="n">
         <v>1000</v>
@@ -32240,7 +32240,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1099" t="n">
         <v>13000</v>
@@ -32269,7 +32269,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1100" t="n">
         <v>2000</v>
@@ -32298,7 +32298,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1106" t="n">
         <v>3000</v>
@@ -32501,7 +32501,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1108" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H1123" t="n">
         <v>1000</v>
@@ -33052,7 +33052,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1127" t="n">
         <v>13000</v>
@@ -33139,7 +33139,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1130" t="n">
         <v>11000</v>
@@ -33168,7 +33168,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33313,7 +33313,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1136" t="n">
         <v>10000</v>
@@ -33342,7 +33342,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1137" t="n">
         <v>8000</v>
@@ -33458,7 +33458,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1141" t="n">
         <v>16000</v>
@@ -33487,7 +33487,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1142" t="n">
         <v>5000</v>
@@ -33516,7 +33516,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1144" t="n">
         <v>5000</v>
@@ -33574,7 +33574,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1151" t="n">
         <v>5000</v>
@@ -33835,7 +33835,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1154" t="n">
         <v>1000</v>
@@ -33864,7 +33864,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1155" t="n">
         <v>12000</v>
@@ -33922,7 +33922,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1157" t="n">
         <v>2000</v>
@@ -43933,6 +43933,35 @@
         <v>10000</v>
       </c>
       <c r="I1502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1503">
+      <c r="A1503" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1503" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1503" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="D1503" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="E1503" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1503" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="G1503" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="H1503" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54134297370911</v>
+        <v>1.54134285449982</v>
       </c>
       <c r="H2" t="n">
         <v>481000</v>
@@ -514,7 +514,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H5" t="n">
         <v>45000</v>
@@ -775,7 +775,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H14" t="n">
         <v>5000</v>
@@ -891,7 +891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H18" t="n">
         <v>4000</v>
@@ -949,7 +949,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741138935089</v>
       </c>
       <c r="H20" t="n">
         <v>86000</v>
@@ -978,7 +978,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45950329303741</v>
+        <v>1.45950317382812</v>
       </c>
       <c r="H21" t="n">
         <v>34000</v>
@@ -1007,7 +1007,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891709804535</v>
+        <v>1.37891721725464</v>
       </c>
       <c r="H22" t="n">
         <v>42000</v>
@@ -1065,7 +1065,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H24" t="n">
         <v>21000</v>
@@ -1326,7 +1326,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G33" t="n">
-        <v>1.52665841579437</v>
+        <v>1.52665829658508</v>
       </c>
       <c r="H33" t="n">
         <v>79000</v>
@@ -1384,7 +1384,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H35" t="n">
         <v>29000</v>
@@ -1413,7 +1413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H36" t="n">
         <v>11000</v>
@@ -1442,7 +1442,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1500,7 +1500,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H39" t="n">
         <v>29000</v>
@@ -1529,7 +1529,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1645,7 +1645,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741138935089</v>
       </c>
       <c r="H44" t="n">
         <v>8000</v>
@@ -1790,7 +1790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H49" t="n">
         <v>25000</v>
@@ -1848,7 +1848,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>1.41025626659393</v>
+        <v>1.41025638580322</v>
       </c>
       <c r="H51" t="n">
         <v>26000</v>
@@ -1935,7 +1935,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G54" t="n">
-        <v>1.45950329303741</v>
+        <v>1.45950317382812</v>
       </c>
       <c r="H54" t="n">
         <v>6000</v>
@@ -2022,7 +2022,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H57" t="n">
         <v>10000</v>
@@ -2080,7 +2080,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398031711578</v>
+        <v>1.46398019790649</v>
       </c>
       <c r="H59" t="n">
         <v>32000</v>
@@ -2138,7 +2138,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2196,7 +2196,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H63" t="n">
         <v>12000</v>
@@ -2312,7 +2312,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473317146301</v>
+        <v>1.41473340988159</v>
       </c>
       <c r="H71" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H72" t="n">
         <v>16000</v>
@@ -2573,7 +2573,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741138935089</v>
       </c>
       <c r="H77" t="n">
         <v>21000</v>
@@ -2631,7 +2631,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398031711578</v>
+        <v>1.46398019790649</v>
       </c>
       <c r="H78" t="n">
         <v>7000</v>
@@ -2660,7 +2660,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H80" t="n">
         <v>2000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2805,7 +2805,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>1.47293424606323</v>
+        <v>1.47293436527252</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2892,7 +2892,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H87" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741138935089</v>
       </c>
       <c r="H89" t="n">
         <v>32000</v>
@@ -2979,7 +2979,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.45950329303741</v>
+        <v>1.45950317382812</v>
       </c>
       <c r="H90" t="n">
         <v>5000</v>
@@ -3037,7 +3037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741138935089</v>
       </c>
       <c r="H92" t="n">
         <v>21000</v>
@@ -3240,7 +3240,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H99" t="n">
         <v>526000</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419201850891</v>
+        <v>2.10419178009033</v>
       </c>
       <c r="H101" t="n">
         <v>211000</v>
@@ -3385,7 +3385,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>2.06837582588196</v>
+        <v>2.06837606430054</v>
       </c>
       <c r="H104" t="n">
         <v>56000</v>
@@ -3414,7 +3414,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674379825592</v>
+        <v>1.99674391746521</v>
       </c>
       <c r="H105" t="n">
         <v>24000</v>
@@ -3443,7 +3443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.0594220161438</v>
+        <v>2.05942177772522</v>
       </c>
       <c r="H106" t="n">
         <v>35000</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H108" t="n">
         <v>40000</v>
@@ -3646,7 +3646,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281203269958</v>
+        <v>2.37281227111816</v>
       </c>
       <c r="H113" t="n">
         <v>108000</v>
@@ -3675,7 +3675,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.4175820350647</v>
+        <v>2.41758227348328</v>
       </c>
       <c r="H114" t="n">
         <v>78000</v>
@@ -3762,7 +3762,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.310133934021</v>
+        <v>2.31013417243958</v>
       </c>
       <c r="H117" t="n">
         <v>66000</v>
@@ -3791,7 +3791,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H118" t="n">
         <v>214000</v>
@@ -3907,7 +3907,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>2.65934038162231</v>
+        <v>2.65934014320374</v>
       </c>
       <c r="H122" t="n">
         <v>118000</v>
@@ -3994,7 +3994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H125" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H127" t="n">
         <v>47000</v>
@@ -4081,7 +4081,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H128" t="n">
         <v>13000</v>
@@ -4110,7 +4110,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561633110046</v>
+        <v>2.60561656951904</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4197,7 +4197,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980013847351</v>
+        <v>2.56980037689209</v>
       </c>
       <c r="H132" t="n">
         <v>46000</v>
@@ -4255,7 +4255,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235227584839</v>
+        <v>2.46235203742981</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H135" t="n">
         <v>50000</v>
@@ -4342,7 +4342,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H137" t="n">
         <v>92000</v>
@@ -43962,6 +43962,35 @@
         <v>3000</v>
       </c>
       <c r="I1503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1504">
+      <c r="A1504" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1504" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1504" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="D1504" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1504" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="F1504" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="G1504" t="n">
+        <v>2.83999991416931</v>
+      </c>
+      <c r="H1504" t="n">
+        <v>2000</v>
+      </c>
+      <c r="I1504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54134285449982</v>
+        <v>1.54134297370911</v>
       </c>
       <c r="H2" t="n">
         <v>481000</v>
@@ -514,7 +514,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H5" t="n">
         <v>45000</v>
@@ -775,7 +775,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H14" t="n">
         <v>5000</v>
@@ -891,7 +891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H18" t="n">
         <v>4000</v>
@@ -949,7 +949,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H20" t="n">
         <v>86000</v>
@@ -978,7 +978,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G21" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H21" t="n">
         <v>34000</v>
@@ -1007,7 +1007,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891721725464</v>
+        <v>1.37891709804535</v>
       </c>
       <c r="H22" t="n">
         <v>42000</v>
@@ -1065,7 +1065,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H24" t="n">
         <v>21000</v>
@@ -1326,7 +1326,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G33" t="n">
-        <v>1.52665829658508</v>
+        <v>1.52665841579437</v>
       </c>
       <c r="H33" t="n">
         <v>79000</v>
@@ -1384,7 +1384,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H35" t="n">
         <v>29000</v>
@@ -1413,7 +1413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H36" t="n">
         <v>11000</v>
@@ -1442,7 +1442,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1500,7 +1500,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H39" t="n">
         <v>29000</v>
@@ -1529,7 +1529,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799734592438</v>
+        <v>1.55799746513367</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1645,7 +1645,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H44" t="n">
         <v>8000</v>
@@ -1790,7 +1790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H49" t="n">
         <v>25000</v>
@@ -1848,7 +1848,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>1.41025638580322</v>
+        <v>1.41025626659393</v>
       </c>
       <c r="H51" t="n">
         <v>26000</v>
@@ -1935,7 +1935,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G54" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H54" t="n">
         <v>6000</v>
@@ -2022,7 +2022,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H57" t="n">
         <v>10000</v>
@@ -2080,7 +2080,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H59" t="n">
         <v>32000</v>
@@ -2138,7 +2138,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2196,7 +2196,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H63" t="n">
         <v>12000</v>
@@ -2312,7 +2312,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473340988159</v>
+        <v>1.41473317146301</v>
       </c>
       <c r="H71" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H72" t="n">
         <v>16000</v>
@@ -2573,7 +2573,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H77" t="n">
         <v>21000</v>
@@ -2631,7 +2631,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H78" t="n">
         <v>7000</v>
@@ -2660,7 +2660,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H80" t="n">
         <v>2000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.4460723400116</v>
+        <v>1.44607222080231</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2805,7 +2805,7 @@
         <v>1.64499998092651</v>
       </c>
       <c r="G84" t="n">
-        <v>1.47293436527252</v>
+        <v>1.47293424606323</v>
       </c>
       <c r="H84" t="n">
         <v>4000</v>
@@ -2892,7 +2892,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159531593323</v>
+        <v>1.44159519672394</v>
       </c>
       <c r="H87" t="n">
         <v>3000</v>
@@ -2950,7 +2950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H89" t="n">
         <v>32000</v>
@@ -2979,7 +2979,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G90" t="n">
-        <v>1.45950317382812</v>
+        <v>1.45950329303741</v>
       </c>
       <c r="H90" t="n">
         <v>5000</v>
@@ -3037,7 +3037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.47741138935089</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H92" t="n">
         <v>21000</v>
@@ -3240,7 +3240,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="n">
         <v>526000</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419178009033</v>
+        <v>2.10419201850891</v>
       </c>
       <c r="H101" t="n">
         <v>211000</v>
@@ -3385,7 +3385,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G104" t="n">
-        <v>2.06837606430054</v>
+        <v>2.06837582588196</v>
       </c>
       <c r="H104" t="n">
         <v>56000</v>
@@ -3414,7 +3414,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674391746521</v>
+        <v>1.99674379825592</v>
       </c>
       <c r="H105" t="n">
         <v>24000</v>
@@ -3443,7 +3443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.05942177772522</v>
+        <v>2.0594220161438</v>
       </c>
       <c r="H106" t="n">
         <v>35000</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="n">
         <v>40000</v>
@@ -3646,7 +3646,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="n">
         <v>108000</v>
@@ -3675,7 +3675,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.41758227348328</v>
+        <v>2.4175820350647</v>
       </c>
       <c r="H114" t="n">
         <v>78000</v>
@@ -3762,7 +3762,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="n">
         <v>66000</v>
@@ -3791,7 +3791,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="n">
         <v>214000</v>
@@ -3907,7 +3907,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G122" t="n">
-        <v>2.65934014320374</v>
+        <v>2.65934038162231</v>
       </c>
       <c r="H122" t="n">
         <v>118000</v>
@@ -3994,7 +3994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="n">
         <v>47000</v>
@@ -4081,7 +4081,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="n">
         <v>13000</v>
@@ -4110,7 +4110,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G129" t="n">
-        <v>2.60561656951904</v>
+        <v>2.60561633110046</v>
       </c>
       <c r="H129" t="n">
         <v>8000</v>
@@ -4197,7 +4197,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G132" t="n">
-        <v>2.56980037689209</v>
+        <v>2.56980013847351</v>
       </c>
       <c r="H132" t="n">
         <v>46000</v>
@@ -4255,7 +4255,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235203742981</v>
+        <v>2.46235227584839</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="n">
         <v>50000</v>
@@ -4342,7 +4342,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="n">
         <v>92000</v>
@@ -43991,6 +43991,35 @@
         <v>2000</v>
       </c>
       <c r="I1504" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1505">
+      <c r="A1505" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1505" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1505" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="D1505" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="E1505" t="n">
+        <v>2.88000011444092</v>
+      </c>
+      <c r="F1505" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="G1505" t="n">
+        <v>2.90000009536743</v>
+      </c>
+      <c r="H1505" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1505" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -456,7 +456,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695139408112</v>
+        <v>1.56695151329041</v>
       </c>
       <c r="H3" t="n">
         <v>153000</v>
@@ -485,7 +485,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G4" t="n">
-        <v>1.56516051292419</v>
+        <v>1.56516063213348</v>
       </c>
       <c r="H4" t="n">
         <v>56000</v>
@@ -601,7 +601,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.5535204410553</v>
+        <v>1.55352032184601</v>
       </c>
       <c r="H8" t="n">
         <v>5000</v>
@@ -630,7 +630,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5535204410553</v>
+        <v>1.55352032184601</v>
       </c>
       <c r="H9" t="n">
         <v>5000</v>
@@ -746,7 +746,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H13" t="n">
         <v>6000</v>
@@ -775,7 +775,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H14" t="n">
         <v>5000</v>
@@ -833,7 +833,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51770436763763</v>
+        <v>1.51770448684692</v>
       </c>
       <c r="H16" t="n">
         <v>93000</v>
@@ -862,7 +862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.522181391716</v>
+        <v>1.52218151092529</v>
       </c>
       <c r="H17" t="n">
         <v>35000</v>
@@ -891,7 +891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H18" t="n">
         <v>4000</v>
@@ -920,7 +920,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H19" t="n">
         <v>4000</v>
@@ -949,7 +949,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741115093231</v>
       </c>
       <c r="H20" t="n">
         <v>86000</v>
@@ -1007,7 +1007,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>1.37891709804535</v>
+        <v>1.37891721725464</v>
       </c>
       <c r="H22" t="n">
         <v>42000</v>
@@ -1094,7 +1094,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G25" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H25" t="n">
         <v>8000</v>
@@ -1181,7 +1181,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>1.51322734355927</v>
+        <v>1.51322746276855</v>
       </c>
       <c r="H28" t="n">
         <v>27000</v>
@@ -1297,7 +1297,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G32" t="n">
-        <v>1.53561234474182</v>
+        <v>1.53561246395111</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1442,7 +1442,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1471,7 +1471,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G38" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H38" t="n">
         <v>29000</v>
@@ -1500,7 +1500,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113532066345</v>
+        <v>1.53113543987274</v>
       </c>
       <c r="H39" t="n">
         <v>29000</v>
@@ -1558,7 +1558,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G41" t="n">
-        <v>1.51770436763763</v>
+        <v>1.51770448684692</v>
       </c>
       <c r="H41" t="n">
         <v>29000</v>
@@ -1616,7 +1616,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48636531829834</v>
+        <v>1.48636519908905</v>
       </c>
       <c r="H43" t="n">
         <v>8000</v>
@@ -1645,7 +1645,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741115093231</v>
       </c>
       <c r="H44" t="n">
         <v>8000</v>
@@ -1674,7 +1674,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H45" t="n">
         <v>196000</v>
@@ -1703,7 +1703,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G46" t="n">
-        <v>1.39234817028046</v>
+        <v>1.39234828948975</v>
       </c>
       <c r="H46" t="n">
         <v>49000</v>
@@ -1732,7 +1732,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.39234817028046</v>
+        <v>1.39234828948975</v>
       </c>
       <c r="H47" t="n">
         <v>99000</v>
@@ -1790,7 +1790,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G49" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H49" t="n">
         <v>25000</v>
@@ -2022,7 +2022,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G57" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H57" t="n">
         <v>10000</v>
@@ -2080,7 +2080,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398031711578</v>
+        <v>1.46398019790649</v>
       </c>
       <c r="H59" t="n">
         <v>32000</v>
@@ -2138,7 +2138,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G61" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H61" t="n">
         <v>21000</v>
@@ -2167,7 +2167,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682507514954</v>
+        <v>1.39682519435883</v>
       </c>
       <c r="H62" t="n">
         <v>6000</v>
@@ -2196,7 +2196,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G63" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H63" t="n">
         <v>12000</v>
@@ -2225,7 +2225,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G64" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H64" t="n">
         <v>4000</v>
@@ -2283,7 +2283,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G66" t="n">
-        <v>1.40577924251556</v>
+        <v>1.40577936172485</v>
       </c>
       <c r="H66" t="n">
         <v>1000</v>
@@ -2312,7 +2312,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G67" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H67" t="n">
         <v>1000</v>
@@ -2341,7 +2341,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G68" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H68" t="n">
         <v>7000</v>
@@ -2370,7 +2370,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G69" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>1.58000004291534</v>
       </c>
       <c r="G71" t="n">
-        <v>1.41473317146301</v>
+        <v>1.4147332906723</v>
       </c>
       <c r="H71" t="n">
         <v>1000</v>
@@ -2457,7 +2457,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G72" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H72" t="n">
         <v>16000</v>
@@ -2602,7 +2602,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741115093231</v>
       </c>
       <c r="H77" t="n">
         <v>21000</v>
@@ -2631,7 +2631,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398031711578</v>
+        <v>1.46398019790649</v>
       </c>
       <c r="H78" t="n">
         <v>7000</v>
@@ -2660,7 +2660,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G79" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H79" t="n">
         <v>6000</v>
@@ -2689,7 +2689,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G80" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H80" t="n">
         <v>2000</v>
@@ -2747,7 +2747,7 @@
         <v>1.61500000953674</v>
       </c>
       <c r="G82" t="n">
-        <v>1.44607222080231</v>
+        <v>1.4460723400116</v>
       </c>
       <c r="H82" t="n">
         <v>6000</v>
@@ -2950,7 +2950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741115093231</v>
       </c>
       <c r="H89" t="n">
         <v>32000</v>
@@ -3037,7 +3037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.4774112701416</v>
+        <v>1.47741115093231</v>
       </c>
       <c r="H92" t="n">
         <v>21000</v>
@@ -3095,7 +3095,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.54008948802948</v>
+        <v>1.54008936882019</v>
       </c>
       <c r="H94" t="n">
         <v>50000</v>
@@ -3182,7 +3182,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G97" t="n">
-        <v>1.59829044342041</v>
+        <v>1.59829032421112</v>
       </c>
       <c r="H97" t="n">
         <v>51000</v>
@@ -3211,7 +3211,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G98" t="n">
-        <v>1.57590544223785</v>
+        <v>1.57590532302856</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H99" t="n">
         <v>526000</v>
@@ -3298,7 +3298,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G101" t="n">
-        <v>2.10419201850891</v>
+        <v>2.10419178009033</v>
       </c>
       <c r="H101" t="n">
         <v>211000</v>
@@ -3327,7 +3327,7 @@
         <v>2.25</v>
       </c>
       <c r="G102" t="n">
-        <v>2.01465177536011</v>
+        <v>2.01465201377869</v>
       </c>
       <c r="H102" t="n">
         <v>176000</v>
@@ -3443,7 +3443,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G106" t="n">
-        <v>2.0594220161438</v>
+        <v>2.05942177772522</v>
       </c>
       <c r="H106" t="n">
         <v>35000</v>
@@ -3472,7 +3472,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>2.13105416297913</v>
+        <v>2.13105392456055</v>
       </c>
       <c r="H107" t="n">
         <v>84000</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000821113586</v>
+        <v>2.14000797271729</v>
       </c>
       <c r="H108" t="n">
         <v>40000</v>
@@ -3588,7 +3588,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48026037216187</v>
+        <v>2.48026013374329</v>
       </c>
       <c r="H111" t="n">
         <v>462000</v>
@@ -3646,7 +3646,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281203269958</v>
+        <v>2.37281227111816</v>
       </c>
       <c r="H113" t="n">
         <v>108000</v>
@@ -3675,7 +3675,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G114" t="n">
-        <v>2.4175820350647</v>
+        <v>2.41758227348328</v>
       </c>
       <c r="H114" t="n">
         <v>78000</v>
@@ -3762,7 +3762,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.310133934021</v>
+        <v>2.31013417243958</v>
       </c>
       <c r="H117" t="n">
         <v>66000</v>
@@ -3791,7 +3791,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H118" t="n">
         <v>214000</v>
@@ -3820,7 +3820,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.47130632400513</v>
+        <v>2.47130608558655</v>
       </c>
       <c r="H119" t="n">
         <v>237000</v>
@@ -3965,7 +3965,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57875442504883</v>
+        <v>2.57875418663025</v>
       </c>
       <c r="H124" t="n">
         <v>27000</v>
@@ -3994,7 +3994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H125" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H127" t="n">
         <v>47000</v>
@@ -4081,7 +4081,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H128" t="n">
         <v>13000</v>
@@ -4139,7 +4139,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>2.57875442504883</v>
+        <v>2.57875418663025</v>
       </c>
       <c r="H130" t="n">
         <v>21000</v>
@@ -4284,7 +4284,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549013137817</v>
+        <v>2.43549036979675</v>
       </c>
       <c r="H135" t="n">
         <v>50000</v>
@@ -4342,7 +4342,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.5966625213623</v>
+        <v>2.59666228294373</v>
       </c>
       <c r="H137" t="n">
         <v>92000</v>
@@ -4429,7 +4429,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.48026037216187</v>
+        <v>2.48026013374329</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>2.48026037216187</v>
+        <v>2.48026013374329</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>2.48026037216187</v>
+        <v>2.48026013374329</v>
       </c>
       <c r="H143" t="n">
         <v>12000</v>
@@ -4545,7 +4545,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.47130632400513</v>
+        <v>2.47130608558655</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4603,7 +4603,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H146" t="n">
         <v>140000</v>
@@ -4661,7 +4661,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H148" t="n">
         <v>71000</v>
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H149" t="n">
         <v>50000</v>
@@ -4748,7 +4748,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H151" t="n">
         <v>330000</v>
@@ -4835,7 +4835,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4980,7 +4980,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H159" t="n">
         <v>18000</v>
@@ -5009,7 +5009,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5212,7 +5212,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H169" t="n">
         <v>9000</v>
@@ -5299,7 +5299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H170" t="n">
         <v>135000</v>
@@ -5357,7 +5357,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H172" t="n">
         <v>6000</v>
@@ -5415,7 +5415,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H174" t="n">
         <v>31000</v>
@@ -5589,7 +5589,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H180" t="n">
         <v>11000</v>
@@ -5763,7 +5763,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H186" t="n">
         <v>5000</v>
@@ -5792,7 +5792,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H187" t="n">
         <v>21000</v>
@@ -5879,7 +5879,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052672386169</v>
+        <v>2.44052696228027</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -6082,7 +6082,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H197" t="n">
         <v>46000</v>
@@ -6140,7 +6140,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H199" t="n">
         <v>70000</v>
@@ -6169,7 +6169,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H200" t="n">
         <v>48000</v>
@@ -6314,7 +6314,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H205" t="n">
         <v>828000</v>
@@ -6372,7 +6372,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H207" t="n">
         <v>89000</v>
@@ -6517,7 +6517,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H212" t="n">
         <v>21000</v>
@@ -6575,7 +6575,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H214" t="n">
         <v>14000</v>
@@ -6604,7 +6604,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H215" t="n">
         <v>9000</v>
@@ -6633,7 +6633,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H216" t="n">
         <v>43000</v>
@@ -6952,7 +6952,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H227" t="n">
         <v>6000</v>
@@ -6981,7 +6981,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H228" t="n">
         <v>2000</v>
@@ -7126,7 +7126,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H233" t="n">
         <v>64000</v>
@@ -7329,7 +7329,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H240" t="n">
         <v>5000</v>
@@ -7358,7 +7358,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H242" t="n">
         <v>14000</v>
@@ -7416,7 +7416,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H243" t="n">
         <v>15000</v>
@@ -7445,7 +7445,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7677,7 +7677,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H252" t="n">
         <v>15000</v>
@@ -7909,7 +7909,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H260" t="n">
         <v>12000</v>
@@ -7996,7 +7996,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H263" t="n">
         <v>5000</v>
@@ -8025,7 +8025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H264" t="n">
         <v>9000</v>
@@ -8083,7 +8083,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8141,7 +8141,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H268" t="n">
         <v>23000</v>
@@ -8170,7 +8170,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.8427107334137</v>
+        <v>2.84271097183228</v>
       </c>
       <c r="H269" t="n">
         <v>11000</v>
@@ -8257,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H273" t="n">
         <v>1000</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H274" t="n">
         <v>9000</v>
@@ -8402,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H277" t="n">
         <v>14000</v>
@@ -8431,7 +8431,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H284" t="n">
         <v>100000</v>
@@ -8721,7 +8721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H288" t="n">
         <v>14000</v>
@@ -8779,7 +8779,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H290" t="n">
         <v>517000</v>
@@ -9040,7 +9040,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H299" t="n">
         <v>8000</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638150215149</v>
+        <v>3.01638126373291</v>
       </c>
       <c r="H301" t="n">
         <v>8000</v>
@@ -9127,7 +9127,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981905937195</v>
+        <v>2.97981929779053</v>
       </c>
       <c r="H302" t="n">
         <v>9000</v>
@@ -9185,7 +9185,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H304" t="n">
         <v>5000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9330,7 +9330,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724101066589</v>
+        <v>3.00724077224731</v>
       </c>
       <c r="H309" t="n">
         <v>134000</v>
@@ -9475,7 +9475,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927341461182</v>
+        <v>2.87927317619324</v>
       </c>
       <c r="H314" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568353652954</v>
+        <v>2.38568329811096</v>
       </c>
       <c r="H330" t="n">
         <v>13000</v>
@@ -10055,7 +10055,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H334" t="n">
         <v>39000</v>
@@ -10142,7 +10142,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H337" t="n">
         <v>4000</v>
@@ -10229,7 +10229,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H340" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H342" t="n">
         <v>4000</v>
@@ -10316,7 +10316,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10548,7 +10548,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10664,7 +10664,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H355" t="n">
         <v>8000</v>
@@ -10867,7 +10867,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H366" t="n">
         <v>3000</v>
@@ -11012,7 +11012,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H367" t="n">
         <v>4000</v>
@@ -11099,7 +11099,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11244,7 +11244,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H375" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H377" t="n">
         <v>5000</v>
@@ -11418,7 +11418,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H381" t="n">
         <v>14000</v>
@@ -11447,7 +11447,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H382" t="n">
         <v>1000</v>
@@ -11476,7 +11476,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958656311035</v>
+        <v>2.76958632469177</v>
       </c>
       <c r="H383" t="n">
         <v>20000</v>
@@ -11621,7 +11621,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H388" t="n">
         <v>4000</v>
@@ -11650,7 +11650,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11737,7 +11737,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H392" t="n">
         <v>3000</v>
@@ -11824,7 +11824,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -12143,7 +12143,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895955085754</v>
+        <v>2.98895978927612</v>
       </c>
       <c r="H406" t="n">
         <v>12000</v>
@@ -12259,7 +12259,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185122489929</v>
+        <v>2.85185146331787</v>
       </c>
       <c r="H410" t="n">
         <v>2000</v>
@@ -12578,7 +12578,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12665,7 +12665,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099195480347</v>
+        <v>2.86099219322205</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12810,7 +12810,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12839,7 +12839,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H430" t="n">
         <v>7000</v>
@@ -12868,7 +12868,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H434" t="n">
         <v>1000</v>
@@ -12984,7 +12984,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H452" t="n">
         <v>2000</v>
@@ -13825,7 +13825,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H464" t="n">
         <v>8000</v>
@@ -14405,7 +14405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H484" t="n">
         <v>10000</v>
@@ -14521,7 +14521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H488" t="n">
         <v>11000</v>
@@ -14579,7 +14579,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14782,7 +14782,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H497" t="n">
         <v>8000</v>
@@ -14811,7 +14811,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H498" t="n">
         <v>22000</v>
@@ -14840,7 +14840,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H506" t="n">
         <v>205000</v>
@@ -15072,7 +15072,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15246,7 +15246,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H513" t="n">
         <v>9000</v>
@@ -15275,7 +15275,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H514" t="n">
         <v>4000</v>
@@ -15304,7 +15304,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H515" t="n">
         <v>3000</v>
@@ -15362,7 +15362,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15565,7 +15565,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15594,7 +15594,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.71474313735962</v>
+        <v>2.7147433757782</v>
       </c>
       <c r="H535" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H536" t="n">
         <v>2000</v>
@@ -16116,7 +16116,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H543" t="n">
         <v>4000</v>
@@ -16232,7 +16232,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216508865356</v>
+        <v>2.74216485023499</v>
       </c>
       <c r="H547" t="n">
         <v>4000</v>
@@ -16406,7 +16406,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H553" t="n">
         <v>2000</v>
@@ -16435,7 +16435,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818117141724</v>
+        <v>2.67818093299866</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849431991577</v>
+        <v>2.56849455833435</v>
       </c>
       <c r="H580" t="n">
         <v>2000</v>
@@ -17479,7 +17479,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H590" t="n">
         <v>3000</v>
@@ -17769,7 +17769,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677554130554</v>
+        <v>2.58677530288696</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17827,7 +17827,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17856,7 +17856,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H603" t="n">
         <v>3000</v>
@@ -17885,7 +17885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H604" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H609" t="n">
         <v>3000</v>
@@ -18059,7 +18059,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H616" t="n">
         <v>7000</v>
@@ -18262,7 +18262,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H621" t="n">
         <v>2000</v>
@@ -18436,7 +18436,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H623" t="n">
         <v>3000</v>
@@ -18465,7 +18465,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279186248779</v>
+        <v>2.52279162406921</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966721534729</v>
+        <v>2.44966745376587</v>
       </c>
       <c r="H631" t="n">
         <v>13000</v>
@@ -18987,7 +18987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H642" t="n">
         <v>5000</v>
@@ -19074,7 +19074,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H645" t="n">
         <v>2000</v>
@@ -19103,7 +19103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H649" t="n">
         <v>9000</v>
@@ -19248,7 +19248,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H651" t="n">
         <v>3000</v>
@@ -19393,7 +19393,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H656" t="n">
         <v>5000</v>
@@ -19422,7 +19422,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.70560264587402</v>
+        <v>2.7056028842926</v>
       </c>
       <c r="H657" t="n">
         <v>7000</v>
@@ -19509,7 +19509,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H660" t="n">
         <v>1000</v>
@@ -19625,7 +19625,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H664" t="n">
         <v>2000</v>
@@ -19654,7 +19654,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H665" t="n">
         <v>7000</v>
@@ -19683,7 +19683,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H666" t="n">
         <v>2000</v>
@@ -19857,7 +19857,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H672" t="n">
         <v>1000</v>
@@ -19886,7 +19886,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H678" t="n">
         <v>2000</v>
@@ -20060,7 +20060,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.63247847557068</v>
+        <v>2.6324782371521</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -21249,7 +21249,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H720" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763481140137</v>
+        <v>2.57763504981995</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H731" t="n">
         <v>9000</v>
@@ -21771,7 +21771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H738" t="n">
         <v>1000</v>
@@ -21800,7 +21800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H739" t="n">
         <v>1000</v>
@@ -21858,7 +21858,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H741" t="n">
         <v>2000</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H742" t="n">
         <v>1000</v>
@@ -21916,7 +21916,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H743" t="n">
         <v>1000</v>
@@ -21945,7 +21945,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H746" t="n">
         <v>1000</v>
@@ -22032,7 +22032,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H747" t="n">
         <v>1000</v>
@@ -22061,7 +22061,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H752" t="n">
         <v>7000</v>
@@ -22206,7 +22206,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H756" t="n">
         <v>5000</v>
@@ -22322,7 +22322,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341839790344</v>
+        <v>2.30341863632202</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H760" t="n">
         <v>7000</v>
@@ -22902,7 +22902,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H777" t="n">
         <v>15000</v>
@@ -23105,7 +23105,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H784" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H787" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H789" t="n">
         <v>23000</v>
@@ -23395,7 +23395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H794" t="n">
         <v>4000</v>
@@ -23424,7 +23424,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H795" t="n">
         <v>5000</v>
@@ -23453,7 +23453,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H797" t="n">
         <v>1000</v>
@@ -23511,7 +23511,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H798" t="n">
         <v>2000</v>
@@ -23540,7 +23540,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H799" t="n">
         <v>1000</v>
@@ -23569,7 +23569,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H800" t="n">
         <v>2000</v>
@@ -23627,7 +23627,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H802" t="n">
         <v>31000</v>
@@ -23743,7 +23743,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H806" t="n">
         <v>1000</v>
@@ -24091,7 +24091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H819" t="n">
         <v>0</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H820" t="n">
         <v>12000</v>
@@ -24468,7 +24468,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H832" t="n">
         <v>67000</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H839" t="n">
         <v>13000</v>
@@ -24729,7 +24729,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24961,7 +24961,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H848" t="n">
         <v>4000</v>
@@ -24990,7 +24990,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H856" t="n">
         <v>13000</v>
@@ -25280,7 +25280,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H859" t="n">
         <v>32000</v>
@@ -25309,7 +25309,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H860" t="n">
         <v>2000</v>
@@ -25367,7 +25367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H862" t="n">
         <v>5000</v>
@@ -25744,7 +25744,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25860,7 +25860,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H879" t="n">
         <v>4000</v>
@@ -26092,7 +26092,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H887" t="n">
         <v>3000</v>
@@ -26121,7 +26121,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H889" t="n">
         <v>5000</v>
@@ -26266,7 +26266,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H893" t="n">
         <v>1000</v>
@@ -26295,7 +26295,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H899" t="n">
         <v>2000</v>
@@ -26556,7 +26556,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H903" t="n">
         <v>1000</v>
@@ -26585,7 +26585,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H907" t="n">
         <v>72000</v>
@@ -26730,7 +26730,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -27078,7 +27078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H921" t="n">
         <v>5000</v>
@@ -27107,7 +27107,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H924" t="n">
         <v>1000</v>
@@ -27194,7 +27194,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H930" t="n">
         <v>3000</v>
@@ -27368,7 +27368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H932" t="n">
         <v>1000</v>
@@ -27426,7 +27426,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27571,7 +27571,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H938" t="n">
         <v>2000</v>
@@ -27600,7 +27600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H961" t="n">
         <v>3000</v>
@@ -28267,7 +28267,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -28325,7 +28325,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -28412,7 +28412,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -28441,7 +28441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.75498557090759</v>
+        <v>1.7549854516983</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -28470,7 +28470,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H969" t="n">
         <v>1000</v>
@@ -28499,7 +28499,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928287506104</v>
+        <v>1.70928275585175</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -28528,7 +28528,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H971" t="n">
         <v>14000</v>
@@ -28557,7 +28557,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28818,7 +28818,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H981" t="n">
         <v>9000</v>
@@ -28963,7 +28963,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H986" t="n">
         <v>4000</v>
@@ -29079,7 +29079,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H990" t="n">
         <v>27000</v>
@@ -29108,7 +29108,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H991" t="n">
         <v>18000</v>
@@ -29224,7 +29224,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H995" t="n">
         <v>21000</v>
@@ -29253,7 +29253,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H996" t="n">
         <v>2000</v>
@@ -29282,7 +29282,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H997" t="n">
         <v>1000</v>
@@ -29311,7 +29311,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1001" t="n">
         <v>19000</v>
@@ -29514,7 +29514,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.2302942276001</v>
+        <v>2.23029398918152</v>
       </c>
       <c r="H1005" t="n">
         <v>11000</v>
@@ -29543,7 +29543,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1006" t="n">
         <v>5000</v>
@@ -29572,7 +29572,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857544898987</v>
+        <v>2.24857521057129</v>
       </c>
       <c r="H1007" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1010" t="n">
         <v>7000</v>
@@ -30123,7 +30123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1026" t="n">
         <v>50000</v>
@@ -30210,7 +30210,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1029" t="n">
         <v>11000</v>
@@ -30297,7 +30297,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1032" t="n">
         <v>20000</v>
@@ -30326,7 +30326,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1033" t="n">
         <v>6000</v>
@@ -30355,7 +30355,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201300621033</v>
+        <v>2.21201324462891</v>
       </c>
       <c r="H1034" t="n">
         <v>12000</v>
@@ -30442,7 +30442,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.1388885974884</v>
+        <v>2.13888835906982</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1048" t="n">
         <v>22000</v>
@@ -30790,7 +30790,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1049" t="n">
         <v>40000</v>
@@ -30964,7 +30964,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1055" t="n">
         <v>7000</v>
@@ -31341,7 +31341,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1068" t="n">
         <v>30000</v>
@@ -31399,7 +31399,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1070" t="n">
         <v>13000</v>
@@ -31428,7 +31428,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -31689,7 +31689,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1080" t="n">
         <v>4000</v>
@@ -31747,7 +31747,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1082" t="n">
         <v>2000</v>
@@ -31776,7 +31776,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1083" t="n">
         <v>10000</v>
@@ -31892,7 +31892,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1087" t="n">
         <v>39000</v>
@@ -31921,7 +31921,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1088" t="n">
         <v>45000</v>
@@ -31950,7 +31950,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1089" t="n">
         <v>19000</v>
@@ -31979,7 +31979,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951537132263</v>
+        <v>1.91951549053192</v>
       </c>
       <c r="H1090" t="n">
         <v>1000</v>
@@ -32240,7 +32240,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1099" t="n">
         <v>13000</v>
@@ -32269,7 +32269,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1100" t="n">
         <v>2000</v>
@@ -32298,7 +32298,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1106" t="n">
         <v>3000</v>
@@ -32501,7 +32501,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1108" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670434951782</v>
+        <v>1.73670446872711</v>
       </c>
       <c r="H1123" t="n">
         <v>1000</v>
@@ -33052,7 +33052,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1127" t="n">
         <v>13000</v>
@@ -33139,7 +33139,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982875823975</v>
+        <v>1.80982887744904</v>
       </c>
       <c r="H1130" t="n">
         <v>11000</v>
@@ -33168,7 +33168,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896948814392</v>
+        <v>1.81896936893463</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33313,7 +33313,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068826675415</v>
+        <v>1.80068838596344</v>
       </c>
       <c r="H1136" t="n">
         <v>10000</v>
@@ -33342,7 +33342,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295328617096</v>
+        <v>1.88295316696167</v>
       </c>
       <c r="H1137" t="n">
         <v>8000</v>
@@ -33458,7 +33458,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1141" t="n">
         <v>16000</v>
@@ -33487,7 +33487,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1142" t="n">
         <v>5000</v>
@@ -33516,7 +33516,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1144" t="n">
         <v>5000</v>
@@ -33574,7 +33574,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435891628265</v>
+        <v>1.97435879707336</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1151" t="n">
         <v>5000</v>
@@ -33835,7 +33835,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404517173767</v>
+        <v>2.08404541015625</v>
       </c>
       <c r="H1154" t="n">
         <v>1000</v>
@@ -33864,7 +33864,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1155" t="n">
         <v>12000</v>
@@ -33922,7 +33922,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748320579529</v>
+        <v>2.04748296737671</v>
       </c>
       <c r="H1157" t="n">
         <v>2000</v>
@@ -44020,6 +44020,35 @@
         <v>3000</v>
       </c>
       <c r="I1505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1506">
+      <c r="A1506" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1506" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1506" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="D1506" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="E1506" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1506" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="G1506" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="H1506" t="n">
+        <v>7000</v>
+      </c>
+      <c r="I1506" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/PMT.MI.xlsx
+++ b/data/PMT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>1.72140002250671</v>
       </c>
       <c r="G2" t="n">
-        <v>1.54134297370911</v>
+        <v>1.54134285449982</v>
       </c>
       <c r="H2" t="n">
         <v>481000</v>
@@ -456,7 +456,7 @@
         <v>1.75</v>
       </c>
       <c r="G3" t="n">
-        <v>1.56695151329041</v>
+        <v>1.56695127487183</v>
       </c>
       <c r="H3" t="n">
         <v>153000</v>
@@ -514,7 +514,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G5" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H5" t="n">
         <v>45000</v>
@@ -601,7 +601,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G8" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H8" t="n">
         <v>5000</v>
@@ -630,7 +630,7 @@
         <v>1.73500001430511</v>
       </c>
       <c r="G9" t="n">
-        <v>1.55352032184601</v>
+        <v>1.5535204410553</v>
       </c>
       <c r="H9" t="n">
         <v>5000</v>
@@ -746,7 +746,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G13" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H13" t="n">
         <v>6000</v>
@@ -775,7 +775,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G14" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H14" t="n">
         <v>5000</v>
@@ -833,7 +833,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G16" t="n">
-        <v>1.51770448684692</v>
+        <v>1.51770436763763</v>
       </c>
       <c r="H16" t="n">
         <v>93000</v>
@@ -862,7 +862,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G17" t="n">
-        <v>1.52218151092529</v>
+        <v>1.522181391716</v>
       </c>
       <c r="H17" t="n">
         <v>35000</v>
@@ -891,7 +891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G18" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H18" t="n">
         <v>4000</v>
@@ -920,7 +920,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G19" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H19" t="n">
         <v>4000</v>
@@ -949,7 +949,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G20" t="n">
-        <v>1.47741115093231</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H20" t="n">
         <v>86000</v>
@@ -1065,7 +1065,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G24" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H24" t="n">
         <v>21000</v>
@@ -1181,7 +1181,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G28" t="n">
-        <v>1.51322746276855</v>
+        <v>1.51322734355927</v>
       </c>
       <c r="H28" t="n">
         <v>27000</v>
@@ -1239,7 +1239,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G30" t="n">
-        <v>1.50427329540253</v>
+        <v>1.50427341461182</v>
       </c>
       <c r="H30" t="n">
         <v>14000</v>
@@ -1297,7 +1297,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G32" t="n">
-        <v>1.53561246395111</v>
+        <v>1.53561234474182</v>
       </c>
       <c r="H32" t="n">
         <v>7000</v>
@@ -1384,7 +1384,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G35" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H35" t="n">
         <v>29000</v>
@@ -1413,7 +1413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G36" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H36" t="n">
         <v>11000</v>
@@ -1442,7 +1442,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G37" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H37" t="n">
         <v>6000</v>
@@ -1471,7 +1471,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G38" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H38" t="n">
         <v>29000</v>
@@ -1500,7 +1500,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G39" t="n">
-        <v>1.53113543987274</v>
+        <v>1.53113532066345</v>
       </c>
       <c r="H39" t="n">
         <v>29000</v>
@@ -1529,7 +1529,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G40" t="n">
-        <v>1.55799746513367</v>
+        <v>1.55799734592438</v>
       </c>
       <c r="H40" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G41" t="n">
-        <v>1.51770448684692</v>
+        <v>1.51770436763763</v>
       </c>
       <c r="H41" t="n">
         <v>29000</v>
@@ -1616,7 +1616,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G43" t="n">
-        <v>1.48636519908905</v>
+        <v>1.48636531829834</v>
       </c>
       <c r="H43" t="n">
         <v>8000</v>
@@ -1645,7 +1645,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G44" t="n">
-        <v>1.47741115093231</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H44" t="n">
         <v>8000</v>
@@ -1674,7 +1674,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G45" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H45" t="n">
         <v>196000</v>
@@ -1703,7 +1703,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G46" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H46" t="n">
         <v>49000</v>
@@ -1732,7 +1732,7 @@
         <v>1.55499994754791</v>
       </c>
       <c r="G47" t="n">
-        <v>1.39234828948975</v>
+        <v>1.39234817028046</v>
       </c>
       <c r="H47" t="n">
         <v>99000</v>
@@ -1848,7 +1848,7 @@
         <v>1.57500004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>1.41025626659393</v>
+        <v>1.41025638580322</v>
       </c>
       <c r="H51" t="n">
         <v>26000</v>
@@ -1877,7 +1877,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G52" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H52" t="n">
         <v>45000</v>
@@ -1906,7 +1906,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G53" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H53" t="n">
         <v>12000</v>
@@ -1993,7 +1993,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G56" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H56" t="n">
         <v>11000</v>
@@ -2080,7 +2080,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G59" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H59" t="n">
         <v>32000</v>
@@ -2167,7 +2167,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G62" t="n">
-        <v>1.39682519435883</v>
+        <v>1.39682507514954</v>
       </c>
       <c r="H62" t="n">
         <v>6000</v>
@@ -2515,7 +2515,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G74" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H74" t="n">
         <v>5000</v>
@@ -2544,7 +2544,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G75" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H75" t="n">
         <v>7000</v>
@@ -2573,7 +2573,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G76" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H76" t="n">
         <v>2000</v>
@@ -2602,7 +2602,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G77" t="n">
-        <v>1.47741115093231</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H77" t="n">
         <v>21000</v>
@@ -2631,7 +2631,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G78" t="n">
-        <v>1.46398019790649</v>
+        <v>1.46398031711578</v>
       </c>
       <c r="H78" t="n">
         <v>7000</v>
@@ -2892,7 +2892,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G87" t="n">
-        <v>1.44159519672394</v>
+        <v>1.44159531593323</v>
       </c>
       <c r="H87" t="n">
         <v>3000</v>
@@ -2921,7 +2921,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G88" t="n">
-        <v>1.45054924488068</v>
+        <v>1.45054936408997</v>
       </c>
       <c r="H88" t="n">
         <v>1000</v>
@@ -2950,7 +2950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G89" t="n">
-        <v>1.47741115093231</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H89" t="n">
         <v>32000</v>
@@ -3037,7 +3037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G92" t="n">
-        <v>1.47741115093231</v>
+        <v>1.4774112701416</v>
       </c>
       <c r="H92" t="n">
         <v>21000</v>
@@ -3095,7 +3095,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G94" t="n">
-        <v>1.54008936882019</v>
+        <v>1.54008948802948</v>
       </c>
       <c r="H94" t="n">
         <v>50000</v>
@@ -3211,7 +3211,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G98" t="n">
-        <v>1.57590532302856</v>
+        <v>1.57590544223785</v>
       </c>
       <c r="H98" t="n">
         <v>13000</v>
@@ -3240,7 +3240,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H99" t="n">
         <v>526000</v>
@@ -3269,7 +3269,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G100" t="n">
-        <v>2.1847779750824</v>
+        <v>2.18477773666382</v>
       </c>
       <c r="H100" t="n">
         <v>722000</v>
@@ -3327,7 +3327,7 @@
         <v>2.25</v>
       </c>
       <c r="G102" t="n">
-        <v>2.01465201377869</v>
+        <v>2.01465177536011</v>
       </c>
       <c r="H102" t="n">
         <v>176000</v>
@@ -3356,7 +3356,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G103" t="n">
-        <v>2.11314582824707</v>
+        <v>2.11314558982849</v>
       </c>
       <c r="H103" t="n">
         <v>123000</v>
@@ -3414,7 +3414,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G105" t="n">
-        <v>1.99674379825592</v>
+        <v>1.9967440366745</v>
       </c>
       <c r="H105" t="n">
         <v>24000</v>
@@ -3472,7 +3472,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G107" t="n">
-        <v>2.13105392456055</v>
+        <v>2.13105416297913</v>
       </c>
       <c r="H107" t="n">
         <v>84000</v>
@@ -3501,7 +3501,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G108" t="n">
-        <v>2.14000797271729</v>
+        <v>2.14000821113586</v>
       </c>
       <c r="H108" t="n">
         <v>40000</v>
@@ -3588,7 +3588,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G111" t="n">
-        <v>2.48026013374329</v>
+        <v>2.48026037216187</v>
       </c>
       <c r="H111" t="n">
         <v>462000</v>
@@ -3646,7 +3646,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G113" t="n">
-        <v>2.37281227111816</v>
+        <v>2.37281203269958</v>
       </c>
       <c r="H113" t="n">
         <v>108000</v>
@@ -3762,7 +3762,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G117" t="n">
-        <v>2.31013417243958</v>
+        <v>2.310133934021</v>
       </c>
       <c r="H117" t="n">
         <v>66000</v>
@@ -3791,7 +3791,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G118" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H118" t="n">
         <v>214000</v>
@@ -3820,7 +3820,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G119" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H119" t="n">
         <v>237000</v>
@@ -3965,7 +3965,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G124" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H124" t="n">
         <v>27000</v>
@@ -3994,7 +3994,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G125" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H125" t="n">
         <v>15000</v>
@@ -4052,7 +4052,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G127" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H127" t="n">
         <v>47000</v>
@@ -4081,7 +4081,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G128" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H128" t="n">
         <v>13000</v>
@@ -4139,7 +4139,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G130" t="n">
-        <v>2.57875418663025</v>
+        <v>2.57875442504883</v>
       </c>
       <c r="H130" t="n">
         <v>21000</v>
@@ -4255,7 +4255,7 @@
         <v>2.75</v>
       </c>
       <c r="G134" t="n">
-        <v>2.46235227584839</v>
+        <v>2.46235203742981</v>
       </c>
       <c r="H134" t="n">
         <v>58000</v>
@@ -4284,7 +4284,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G135" t="n">
-        <v>2.43549036979675</v>
+        <v>2.43549013137817</v>
       </c>
       <c r="H135" t="n">
         <v>50000</v>
@@ -4342,7 +4342,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59666228294373</v>
+        <v>2.5966625213623</v>
       </c>
       <c r="H137" t="n">
         <v>92000</v>
@@ -4429,7 +4429,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G140" t="n">
-        <v>2.48026013374329</v>
+        <v>2.48026037216187</v>
       </c>
       <c r="H140" t="n">
         <v>9000</v>
@@ -4458,7 +4458,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G141" t="n">
-        <v>2.48026013374329</v>
+        <v>2.48026037216187</v>
       </c>
       <c r="H141" t="n">
         <v>5000</v>
@@ -4516,7 +4516,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G143" t="n">
-        <v>2.48026013374329</v>
+        <v>2.48026037216187</v>
       </c>
       <c r="H143" t="n">
         <v>12000</v>
@@ -4545,7 +4545,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.47130608558655</v>
+        <v>2.47130632400513</v>
       </c>
       <c r="H144" t="n">
         <v>6000</v>
@@ -4603,7 +4603,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G146" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H146" t="n">
         <v>140000</v>
@@ -4661,7 +4661,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H148" t="n">
         <v>71000</v>
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H149" t="n">
         <v>50000</v>
@@ -4748,7 +4748,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G151" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H151" t="n">
         <v>330000</v>
@@ -4835,7 +4835,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G154" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4980,7 +4980,7 @@
         <v>3</v>
       </c>
       <c r="G159" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H159" t="n">
         <v>18000</v>
@@ -5009,7 +5009,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G160" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H160" t="n">
         <v>4000</v>
@@ -5038,7 +5038,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H161" t="n">
         <v>7000</v>
@@ -5212,7 +5212,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H167" t="n">
         <v>10000</v>
@@ -5270,7 +5270,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G169" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H169" t="n">
         <v>9000</v>
@@ -5299,7 +5299,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G170" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H170" t="n">
         <v>135000</v>
@@ -5357,7 +5357,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G172" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H172" t="n">
         <v>6000</v>
@@ -5415,7 +5415,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G174" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H174" t="n">
         <v>31000</v>
@@ -5589,7 +5589,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G180" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H180" t="n">
         <v>11000</v>
@@ -5763,7 +5763,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G186" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H186" t="n">
         <v>5000</v>
@@ -5792,7 +5792,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G187" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H187" t="n">
         <v>21000</v>
@@ -5879,7 +5879,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G190" t="n">
-        <v>2.44052696228027</v>
+        <v>2.44052672386169</v>
       </c>
       <c r="H190" t="n">
         <v>4000</v>
@@ -6082,7 +6082,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G197" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H197" t="n">
         <v>46000</v>
@@ -6140,7 +6140,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G199" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H199" t="n">
         <v>70000</v>
@@ -6169,7 +6169,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G200" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H200" t="n">
         <v>48000</v>
@@ -6314,7 +6314,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G205" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H205" t="n">
         <v>828000</v>
@@ -6372,7 +6372,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G207" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H207" t="n">
         <v>89000</v>
@@ -6517,7 +6517,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G212" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H212" t="n">
         <v>21000</v>
@@ -6575,7 +6575,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G214" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H214" t="n">
         <v>14000</v>
@@ -6604,7 +6604,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G215" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H215" t="n">
         <v>9000</v>
@@ -6633,7 +6633,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G216" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H216" t="n">
         <v>43000</v>
@@ -6952,7 +6952,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G227" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H227" t="n">
         <v>6000</v>
@@ -6981,7 +6981,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G228" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H228" t="n">
         <v>2000</v>
@@ -7126,7 +7126,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G233" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H233" t="n">
         <v>64000</v>
@@ -7329,7 +7329,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G240" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H240" t="n">
         <v>5000</v>
@@ -7358,7 +7358,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G241" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G242" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H242" t="n">
         <v>14000</v>
@@ -7416,7 +7416,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G243" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H243" t="n">
         <v>15000</v>
@@ -7445,7 +7445,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G244" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H244" t="n">
         <v>12000</v>
@@ -7677,7 +7677,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G252" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H252" t="n">
         <v>15000</v>
@@ -7909,7 +7909,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G260" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H260" t="n">
         <v>12000</v>
@@ -7996,7 +7996,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G263" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H263" t="n">
         <v>5000</v>
@@ -8025,7 +8025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H264" t="n">
         <v>9000</v>
@@ -8083,7 +8083,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G266" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H266" t="n">
         <v>2000</v>
@@ -8141,7 +8141,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G268" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H268" t="n">
         <v>23000</v>
@@ -8170,7 +8170,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G269" t="n">
-        <v>2.84271097183228</v>
+        <v>2.8427107334137</v>
       </c>
       <c r="H269" t="n">
         <v>11000</v>
@@ -8257,7 +8257,7 @@
         <v>3</v>
       </c>
       <c r="G272" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H272" t="n">
         <v>11000</v>
@@ -8286,7 +8286,7 @@
         <v>3</v>
       </c>
       <c r="G273" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H273" t="n">
         <v>1000</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H274" t="n">
         <v>9000</v>
@@ -8402,7 +8402,7 @@
         <v>3</v>
       </c>
       <c r="G277" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H277" t="n">
         <v>14000</v>
@@ -8431,7 +8431,7 @@
         <v>3</v>
       </c>
       <c r="G278" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H278" t="n">
         <v>2000</v>
@@ -8605,7 +8605,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G284" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H284" t="n">
         <v>100000</v>
@@ -8721,7 +8721,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G288" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H288" t="n">
         <v>14000</v>
@@ -8779,7 +8779,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G290" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H290" t="n">
         <v>517000</v>
@@ -9040,7 +9040,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H299" t="n">
         <v>8000</v>
@@ -9098,7 +9098,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G301" t="n">
-        <v>3.01638126373291</v>
+        <v>3.01638150215149</v>
       </c>
       <c r="H301" t="n">
         <v>8000</v>
@@ -9127,7 +9127,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G302" t="n">
-        <v>2.97981929779053</v>
+        <v>2.97981905937195</v>
       </c>
       <c r="H302" t="n">
         <v>9000</v>
@@ -9185,7 +9185,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G304" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H304" t="n">
         <v>5000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G307" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H307" t="n">
         <v>16000</v>
@@ -9330,7 +9330,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G309" t="n">
-        <v>3.00724077224731</v>
+        <v>3.00724101066589</v>
       </c>
       <c r="H309" t="n">
         <v>134000</v>
@@ -9475,7 +9475,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G314" t="n">
-        <v>2.87927317619324</v>
+        <v>2.87927341461182</v>
       </c>
       <c r="H314" t="n">
         <v>5000</v>
@@ -9939,7 +9939,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G330" t="n">
-        <v>2.38568329811096</v>
+        <v>2.38568353652954</v>
       </c>
       <c r="H330" t="n">
         <v>13000</v>
@@ -10055,7 +10055,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G334" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H334" t="n">
         <v>39000</v>
@@ -10142,7 +10142,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G337" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H337" t="n">
         <v>4000</v>
@@ -10229,7 +10229,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G340" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H340" t="n">
         <v>5000</v>
@@ -10287,7 +10287,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G342" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H342" t="n">
         <v>4000</v>
@@ -10316,7 +10316,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G343" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H343" t="n">
         <v>0</v>
@@ -10374,7 +10374,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G345" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H345" t="n">
         <v>2000</v>
@@ -10548,7 +10548,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G351" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H351" t="n">
         <v>5000</v>
@@ -10577,7 +10577,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G352" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H352" t="n">
         <v>8000</v>
@@ -10664,7 +10664,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G355" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H355" t="n">
         <v>8000</v>
@@ -10867,7 +10867,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G362" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H362" t="n">
         <v>3000</v>
@@ -10983,7 +10983,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G366" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H366" t="n">
         <v>3000</v>
@@ -11012,7 +11012,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G367" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H367" t="n">
         <v>4000</v>
@@ -11099,7 +11099,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G370" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11244,7 +11244,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G375" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H375" t="n">
         <v>2000</v>
@@ -11302,7 +11302,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G377" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H377" t="n">
         <v>5000</v>
@@ -11418,7 +11418,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G381" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H381" t="n">
         <v>14000</v>
@@ -11447,7 +11447,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G382" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H382" t="n">
         <v>1000</v>
@@ -11476,7 +11476,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G383" t="n">
-        <v>2.76958632469177</v>
+        <v>2.76958656311035</v>
       </c>
       <c r="H383" t="n">
         <v>20000</v>
@@ -11621,7 +11621,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G388" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H388" t="n">
         <v>4000</v>
@@ -11650,7 +11650,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G389" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H389" t="n">
         <v>6000</v>
@@ -11737,7 +11737,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G392" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H392" t="n">
         <v>3000</v>
@@ -11824,7 +11824,7 @@
         <v>3</v>
       </c>
       <c r="G395" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -12143,7 +12143,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G406" t="n">
-        <v>2.98895978927612</v>
+        <v>2.98895955085754</v>
       </c>
       <c r="H406" t="n">
         <v>12000</v>
@@ -12259,7 +12259,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G410" t="n">
-        <v>2.85185146331787</v>
+        <v>2.85185122489929</v>
       </c>
       <c r="H410" t="n">
         <v>2000</v>
@@ -12578,7 +12578,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G421" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H421" t="n">
         <v>2000</v>
@@ -12665,7 +12665,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G424" t="n">
-        <v>2.86099219322205</v>
+        <v>2.86099195480347</v>
       </c>
       <c r="H424" t="n">
         <v>2000</v>
@@ -12810,7 +12810,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G429" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H429" t="n">
         <v>1000</v>
@@ -12839,7 +12839,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G430" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H430" t="n">
         <v>7000</v>
@@ -12868,7 +12868,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G431" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G432" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H432" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H433" t="n">
         <v>0</v>
@@ -12955,7 +12955,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G434" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H434" t="n">
         <v>1000</v>
@@ -12984,7 +12984,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G435" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
         <v>3</v>
       </c>
       <c r="G448" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H448" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3</v>
       </c>
       <c r="G449" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H449" t="n">
         <v>0</v>
@@ -13477,7 +13477,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G452" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H452" t="n">
         <v>2000</v>
@@ -13825,7 +13825,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G464" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H464" t="n">
         <v>8000</v>
@@ -14405,7 +14405,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G484" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H484" t="n">
         <v>10000</v>
@@ -14521,7 +14521,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G488" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H488" t="n">
         <v>11000</v>
@@ -14579,7 +14579,7 @@
         <v>3</v>
       </c>
       <c r="G490" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H490" t="n">
         <v>3000</v>
@@ -14782,7 +14782,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G497" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H497" t="n">
         <v>8000</v>
@@ -14811,7 +14811,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G498" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H498" t="n">
         <v>22000</v>
@@ -14840,7 +14840,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G499" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H499" t="n">
         <v>5000</v>
@@ -15043,7 +15043,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G506" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H506" t="n">
         <v>205000</v>
@@ -15072,7 +15072,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G507" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15246,7 +15246,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G513" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H513" t="n">
         <v>9000</v>
@@ -15275,7 +15275,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G514" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H514" t="n">
         <v>4000</v>
@@ -15304,7 +15304,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G515" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H515" t="n">
         <v>3000</v>
@@ -15362,7 +15362,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G517" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H517" t="n">
         <v>2000</v>
@@ -15565,7 +15565,7 @@
         <v>3</v>
       </c>
       <c r="G524" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H524" t="n">
         <v>14000</v>
@@ -15594,7 +15594,7 @@
         <v>3</v>
       </c>
       <c r="G525" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H525" t="n">
         <v>0</v>
@@ -15884,7 +15884,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G535" t="n">
-        <v>2.7147433757782</v>
+        <v>2.71474313735962</v>
       </c>
       <c r="H535" t="n">
         <v>6000</v>
@@ -15913,7 +15913,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H536" t="n">
         <v>2000</v>
@@ -16116,7 +16116,7 @@
         <v>3</v>
       </c>
       <c r="G543" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H543" t="n">
         <v>4000</v>
@@ -16232,7 +16232,7 @@
         <v>3</v>
       </c>
       <c r="G547" t="n">
-        <v>2.74216485023499</v>
+        <v>2.74216508865356</v>
       </c>
       <c r="H547" t="n">
         <v>4000</v>
@@ -16406,7 +16406,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G553" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H553" t="n">
         <v>2000</v>
@@ -16435,7 +16435,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G554" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H554" t="n">
         <v>0</v>
@@ -16464,7 +16464,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G555" t="n">
-        <v>2.67818093299866</v>
+        <v>2.67818117141724</v>
       </c>
       <c r="H555" t="n">
         <v>0</v>
@@ -16522,7 +16522,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G557" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H557" t="n">
         <v>1000</v>
@@ -16551,7 +16551,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G558" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H558" t="n">
         <v>0</v>
@@ -17189,7 +17189,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G580" t="n">
-        <v>2.56849455833435</v>
+        <v>2.56849431991577</v>
       </c>
       <c r="H580" t="n">
         <v>2000</v>
@@ -17479,7 +17479,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G590" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H590" t="n">
         <v>3000</v>
@@ -17769,7 +17769,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G600" t="n">
-        <v>2.58677530288696</v>
+        <v>2.58677554130554</v>
       </c>
       <c r="H600" t="n">
         <v>9000</v>
@@ -17827,7 +17827,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G602" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H602" t="n">
         <v>5000</v>
@@ -17856,7 +17856,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G603" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H603" t="n">
         <v>3000</v>
@@ -17885,7 +17885,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G604" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H604" t="n">
         <v>1000</v>
@@ -18030,7 +18030,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G609" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H609" t="n">
         <v>3000</v>
@@ -18059,7 +18059,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H610" t="n">
         <v>0</v>
@@ -18233,7 +18233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G616" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H616" t="n">
         <v>7000</v>
@@ -18262,7 +18262,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G617" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H617" t="n">
         <v>0</v>
@@ -18378,7 +18378,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G621" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H621" t="n">
         <v>2000</v>
@@ -18436,7 +18436,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G623" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H623" t="n">
         <v>3000</v>
@@ -18465,7 +18465,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G624" t="n">
-        <v>2.52279162406921</v>
+        <v>2.52279186248779</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G631" t="n">
-        <v>2.44966745376587</v>
+        <v>2.44966721534729</v>
       </c>
       <c r="H631" t="n">
         <v>13000</v>
@@ -18987,7 +18987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G642" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H642" t="n">
         <v>5000</v>
@@ -19074,7 +19074,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G645" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H645" t="n">
         <v>2000</v>
@@ -19103,7 +19103,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G646" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H646" t="n">
         <v>0</v>
@@ -19190,7 +19190,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G649" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H649" t="n">
         <v>9000</v>
@@ -19248,7 +19248,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H651" t="n">
         <v>3000</v>
@@ -19393,7 +19393,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G656" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H656" t="n">
         <v>5000</v>
@@ -19422,7 +19422,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G657" t="n">
-        <v>2.7056028842926</v>
+        <v>2.70560264587402</v>
       </c>
       <c r="H657" t="n">
         <v>7000</v>
@@ -19509,7 +19509,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G660" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H660" t="n">
         <v>1000</v>
@@ -19625,7 +19625,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G664" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H664" t="n">
         <v>2000</v>
@@ -19654,7 +19654,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G665" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H665" t="n">
         <v>7000</v>
@@ -19683,7 +19683,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G666" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H666" t="n">
         <v>2000</v>
@@ -19857,7 +19857,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G672" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H672" t="n">
         <v>1000</v>
@@ -19886,7 +19886,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G673" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H673" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G678" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H678" t="n">
         <v>2000</v>
@@ -20060,7 +20060,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G679" t="n">
-        <v>2.6324782371521</v>
+        <v>2.63247847557068</v>
       </c>
       <c r="H679" t="n">
         <v>0</v>
@@ -20901,7 +20901,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G708" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H708" t="n">
         <v>4000</v>
@@ -21249,7 +21249,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G720" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H720" t="n">
         <v>2000</v>
@@ -21278,7 +21278,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G721" t="n">
-        <v>2.57763504981995</v>
+        <v>2.57763481140137</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H731" t="n">
         <v>9000</v>
@@ -21771,7 +21771,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G738" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H738" t="n">
         <v>1000</v>
@@ -21800,7 +21800,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G739" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H739" t="n">
         <v>1000</v>
@@ -21858,7 +21858,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G741" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H741" t="n">
         <v>2000</v>
@@ -21887,7 +21887,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G742" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H742" t="n">
         <v>1000</v>
@@ -21916,7 +21916,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H743" t="n">
         <v>1000</v>
@@ -21945,7 +21945,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G744" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H744" t="n">
         <v>0</v>
@@ -21974,7 +21974,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H745" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G746" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H746" t="n">
         <v>1000</v>
@@ -22032,7 +22032,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G747" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H747" t="n">
         <v>1000</v>
@@ -22061,7 +22061,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H748" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G749" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H749" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H750" t="n">
         <v>0</v>
@@ -22148,7 +22148,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H751" t="n">
         <v>0</v>
@@ -22177,7 +22177,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G752" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H752" t="n">
         <v>7000</v>
@@ -22206,7 +22206,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G753" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H753" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H756" t="n">
         <v>5000</v>
@@ -22322,7 +22322,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G757" t="n">
-        <v>2.30341863632202</v>
+        <v>2.30341839790344</v>
       </c>
       <c r="H757" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G760" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H760" t="n">
         <v>7000</v>
@@ -22902,7 +22902,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G777" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H777" t="n">
         <v>15000</v>
@@ -23105,7 +23105,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G784" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H784" t="n">
         <v>2000</v>
@@ -23192,7 +23192,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H787" t="n">
         <v>4000</v>
@@ -23250,7 +23250,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G789" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H789" t="n">
         <v>23000</v>
@@ -23395,7 +23395,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H794" t="n">
         <v>4000</v>
@@ -23424,7 +23424,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G795" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H795" t="n">
         <v>5000</v>
@@ -23453,7 +23453,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G796" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H796" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G797" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H797" t="n">
         <v>1000</v>
@@ -23511,7 +23511,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G798" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H798" t="n">
         <v>2000</v>
@@ -23540,7 +23540,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G799" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H799" t="n">
         <v>1000</v>
@@ -23569,7 +23569,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G800" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H800" t="n">
         <v>2000</v>
@@ -23627,7 +23627,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G802" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H802" t="n">
         <v>31000</v>
@@ -23743,7 +23743,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G806" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H806" t="n">
         <v>1000</v>
@@ -24091,7 +24091,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G818" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H818" t="n">
         <v>2000</v>
@@ -24120,7 +24120,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G819" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H819" t="n">
         <v>0</v>
@@ -24149,7 +24149,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G820" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H820" t="n">
         <v>12000</v>
@@ -24468,7 +24468,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G831" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H831" t="n">
         <v>1000</v>
@@ -24497,7 +24497,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G832" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H832" t="n">
         <v>67000</v>
@@ -24700,7 +24700,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G839" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H839" t="n">
         <v>13000</v>
@@ -24729,7 +24729,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G840" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H840" t="n">
         <v>0</v>
@@ -24961,7 +24961,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G848" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H848" t="n">
         <v>4000</v>
@@ -24990,7 +24990,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G849" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H849" t="n">
         <v>0</v>
@@ -25193,7 +25193,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G856" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H856" t="n">
         <v>13000</v>
@@ -25280,7 +25280,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H859" t="n">
         <v>32000</v>
@@ -25309,7 +25309,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G860" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H860" t="n">
         <v>2000</v>
@@ -25367,7 +25367,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H862" t="n">
         <v>5000</v>
@@ -25744,7 +25744,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G875" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H875" t="n">
         <v>3000</v>
@@ -25860,7 +25860,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G879" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H879" t="n">
         <v>4000</v>
@@ -26092,7 +26092,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H887" t="n">
         <v>3000</v>
@@ -26121,7 +26121,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G888" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H888" t="n">
         <v>0</v>
@@ -26150,7 +26150,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G889" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H889" t="n">
         <v>5000</v>
@@ -26266,7 +26266,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H893" t="n">
         <v>1000</v>
@@ -26295,7 +26295,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G894" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H894" t="n">
         <v>0</v>
@@ -26440,7 +26440,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G899" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H899" t="n">
         <v>2000</v>
@@ -26556,7 +26556,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G903" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H903" t="n">
         <v>1000</v>
@@ -26585,7 +26585,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G904" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H904" t="n">
         <v>1000</v>
@@ -26614,7 +26614,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G905" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H905" t="n">
         <v>0</v>
@@ -26672,7 +26672,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G907" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H907" t="n">
         <v>72000</v>
@@ -26730,7 +26730,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G909" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H909" t="n">
         <v>18000</v>
@@ -27078,7 +27078,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G921" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H921" t="n">
         <v>5000</v>
@@ -27107,7 +27107,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G922" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27136,7 +27136,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H923" t="n">
         <v>0</v>
@@ -27165,7 +27165,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H924" t="n">
         <v>1000</v>
@@ -27194,7 +27194,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G925" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H925" t="n">
         <v>3000</v>
@@ -27223,7 +27223,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H926" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H927" t="n">
         <v>0</v>
@@ -27339,7 +27339,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G930" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H930" t="n">
         <v>3000</v>
@@ -27368,7 +27368,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G931" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G932" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H932" t="n">
         <v>1000</v>
@@ -27426,7 +27426,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G933" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H933" t="n">
         <v>0</v>
@@ -27513,7 +27513,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G936" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H936" t="n">
         <v>6000</v>
@@ -27571,7 +27571,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G938" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H938" t="n">
         <v>2000</v>
@@ -27600,7 +27600,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G939" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H939" t="n">
         <v>0</v>
@@ -27629,7 +27629,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G940" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H940" t="n">
         <v>3000</v>
@@ -28238,7 +28238,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G961" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H961" t="n">
         <v>3000</v>
@@ -28267,7 +28267,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G962" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H962" t="n">
         <v>0</v>
@@ -28296,7 +28296,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G963" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H963" t="n">
         <v>0</v>
@@ -28325,7 +28325,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G964" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H964" t="n">
         <v>0</v>
@@ -28354,7 +28354,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G965" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H965" t="n">
         <v>0</v>
@@ -28383,7 +28383,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G966" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H966" t="n">
         <v>0</v>
@@ -28412,7 +28412,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G967" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H967" t="n">
         <v>0</v>
@@ -28441,7 +28441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G968" t="n">
-        <v>1.7549854516983</v>
+        <v>1.75498557090759</v>
       </c>
       <c r="H968" t="n">
         <v>0</v>
@@ -28470,7 +28470,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G969" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H969" t="n">
         <v>1000</v>
@@ -28499,7 +28499,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G970" t="n">
-        <v>1.70928275585175</v>
+        <v>1.70928287506104</v>
       </c>
       <c r="H970" t="n">
         <v>0</v>
@@ -28528,7 +28528,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G971" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H971" t="n">
         <v>14000</v>
@@ -28557,7 +28557,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G972" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H972" t="n">
         <v>2000</v>
@@ -28731,7 +28731,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G978" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28818,7 +28818,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G981" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H981" t="n">
         <v>9000</v>
@@ -28963,7 +28963,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G986" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H986" t="n">
         <v>4000</v>
@@ -29079,7 +29079,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G990" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H990" t="n">
         <v>27000</v>
@@ -29108,7 +29108,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G991" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H991" t="n">
         <v>18000</v>
@@ -29224,7 +29224,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G995" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H995" t="n">
         <v>21000</v>
@@ -29253,7 +29253,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G996" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H996" t="n">
         <v>2000</v>
@@ -29282,7 +29282,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H997" t="n">
         <v>1000</v>
@@ -29311,7 +29311,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H998" t="n">
         <v>0</v>
@@ -29340,7 +29340,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G999" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H999" t="n">
         <v>6000</v>
@@ -29369,7 +29369,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1000" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1001" t="n">
         <v>19000</v>
@@ -29514,7 +29514,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.23029398918152</v>
+        <v>2.2302942276001</v>
       </c>
       <c r="H1005" t="n">
         <v>11000</v>
@@ -29543,7 +29543,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1006" t="n">
         <v>5000</v>
@@ -29572,7 +29572,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.24857521057129</v>
+        <v>2.24857544898987</v>
       </c>
       <c r="H1007" t="n">
         <v>6000</v>
@@ -29659,7 +29659,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1010" t="n">
         <v>7000</v>
@@ -30123,7 +30123,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1026" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1026" t="n">
         <v>50000</v>
@@ -30210,7 +30210,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1029" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1029" t="n">
         <v>11000</v>
@@ -30297,7 +30297,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1032" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1032" t="n">
         <v>20000</v>
@@ -30326,7 +30326,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1033" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1033" t="n">
         <v>6000</v>
@@ -30355,7 +30355,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1034" t="n">
-        <v>2.21201324462891</v>
+        <v>2.21201300621033</v>
       </c>
       <c r="H1034" t="n">
         <v>12000</v>
@@ -30442,7 +30442,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1037" t="n">
-        <v>2.13888835906982</v>
+        <v>2.1388885974884</v>
       </c>
       <c r="H1037" t="n">
         <v>3000</v>
@@ -30761,7 +30761,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1048" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1048" t="n">
         <v>22000</v>
@@ -30790,7 +30790,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1049" t="n">
         <v>40000</v>
@@ -30964,7 +30964,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1055" t="n">
         <v>7000</v>
@@ -31341,7 +31341,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1068" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1068" t="n">
         <v>30000</v>
@@ -31399,7 +31399,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1070" t="n">
         <v>13000</v>
@@ -31428,7 +31428,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1071" t="n">
         <v>0</v>
@@ -31689,7 +31689,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1080" t="n">
         <v>4000</v>
@@ -31747,7 +31747,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1082" t="n">
         <v>2000</v>
@@ -31776,7 +31776,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1083" t="n">
         <v>10000</v>
@@ -31892,7 +31892,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1087" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1087" t="n">
         <v>39000</v>
@@ -31921,7 +31921,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1088" t="n">
         <v>45000</v>
@@ -31950,7 +31950,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1089" t="n">
         <v>19000</v>
@@ -31979,7 +31979,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.91951549053192</v>
+        <v>1.91951537132263</v>
       </c>
       <c r="H1090" t="n">
         <v>1000</v>
@@ -32240,7 +32240,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1099" t="n">
         <v>13000</v>
@@ -32269,7 +32269,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1100" t="n">
         <v>2000</v>
@@ -32298,7 +32298,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1101" t="n">
         <v>0</v>
@@ -32443,7 +32443,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1106" t="n">
         <v>3000</v>
@@ -32501,7 +32501,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1108" t="n">
         <v>2000</v>
@@ -32936,7 +32936,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.73670446872711</v>
+        <v>1.73670434951782</v>
       </c>
       <c r="H1123" t="n">
         <v>1000</v>
@@ -33052,7 +33052,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1127" t="n">
         <v>13000</v>
@@ -33139,7 +33139,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.80982887744904</v>
+        <v>1.80982875823975</v>
       </c>
       <c r="H1130" t="n">
         <v>11000</v>
@@ -33168,7 +33168,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.81896936893463</v>
+        <v>1.81896948814392</v>
       </c>
       <c r="H1131" t="n">
         <v>5000</v>
@@ -33313,7 +33313,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.80068838596344</v>
+        <v>1.80068826675415</v>
       </c>
       <c r="H1136" t="n">
         <v>10000</v>
@@ -33342,7 +33342,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.88295316696167</v>
+        <v>1.88295328617096</v>
       </c>
       <c r="H1137" t="n">
         <v>8000</v>
@@ -33458,7 +33458,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1141" t="n">
         <v>16000</v>
@@ -33487,7 +33487,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1142" t="n">
         <v>5000</v>
@@ -33516,7 +33516,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1143" t="n">
         <v>2000</v>
@@ -33545,7 +33545,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1144" t="n">
         <v>5000</v>
@@ -33574,7 +33574,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.97435879707336</v>
+        <v>1.97435891628265</v>
       </c>
       <c r="H1145" t="n">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1151" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1151" t="n">
         <v>5000</v>
@@ -33835,7 +33835,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1154" t="n">
-        <v>2.08404541015625</v>
+        <v>2.08404517173767</v>
       </c>
       <c r="H1154" t="n">
         <v>1000</v>
@@ -33864,7 +33864,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1155" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1155" t="n">
         <v>12000</v>
@@ -33922,7 +33922,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1157" t="n">
-        <v>2.04748296737671</v>
+        <v>2.04748320579529</v>
       </c>
       <c r="H1157" t="n">
         <v>2000</v>
@@ -44049,6 +44049,35 @@
         <v>7000</v>
       </c>
       <c r="I1506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1507">
+      <c r="A1507" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1507" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1507" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="D1507" t="n">
+        <v>2.96000003814697</v>
+      </c>
+      <c r="E1507" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="F1507" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="G1507" t="n">
+        <v>2.92000007629395</v>
+      </c>
+      <c r="H1507" t="n">
+        <v>3000</v>
+      </c>
+      <c r="I1507" t="s">
         <v>9</v>
       </c>
     </row>
